--- a/data/nzd0043/nzd0043.xlsx
+++ b/data/nzd0043/nzd0043.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P522"/>
+  <dimension ref="A1:P523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28618,6 +28618,60 @@
         <v>331.6</v>
       </c>
       <c r="P522" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>336.95</v>
+      </c>
+      <c r="C523" t="n">
+        <v>332.92</v>
+      </c>
+      <c r="D523" t="n">
+        <v>341.98</v>
+      </c>
+      <c r="E523" t="n">
+        <v>350.31</v>
+      </c>
+      <c r="F523" t="n">
+        <v>338.33</v>
+      </c>
+      <c r="G523" t="n">
+        <v>336.12</v>
+      </c>
+      <c r="H523" t="n">
+        <v>342.02</v>
+      </c>
+      <c r="I523" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="J523" t="n">
+        <v>342.59</v>
+      </c>
+      <c r="K523" t="n">
+        <v>349.37</v>
+      </c>
+      <c r="L523" t="n">
+        <v>350.74</v>
+      </c>
+      <c r="M523" t="n">
+        <v>337.94</v>
+      </c>
+      <c r="N523" t="n">
+        <v>319.52</v>
+      </c>
+      <c r="O523" t="n">
+        <v>330.22</v>
+      </c>
+      <c r="P523" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -28634,7 +28688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B529"/>
+  <dimension ref="A1:B530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33927,6 +33981,16 @@
       </c>
       <c r="B529" t="n">
         <v>-0.47</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -34095,28 +34159,28 @@
         <v>0.0638</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.005635897627020733</v>
+        <v>-0.009007141853605471</v>
       </c>
       <c r="J2" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K2" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L2" t="n">
-        <v>7.271825672361398e-05</v>
+        <v>0.0001852873971764923</v>
       </c>
       <c r="M2" t="n">
-        <v>4.112999835564897</v>
+        <v>4.121536825644862</v>
       </c>
       <c r="N2" t="n">
-        <v>25.55169665646785</v>
+        <v>25.66579325092926</v>
       </c>
       <c r="O2" t="n">
-        <v>5.054868609219023</v>
+        <v>5.066141850652157</v>
       </c>
       <c r="P2" t="n">
-        <v>346.3517208804034</v>
+        <v>346.3849388299884</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34173,28 +34237,28 @@
         <v>0.0634</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.006748884174736474</v>
+        <v>-0.009400216871346161</v>
       </c>
       <c r="J3" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K3" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000119062062892028</v>
+        <v>0.0002308613994312925</v>
       </c>
       <c r="M3" t="n">
-        <v>3.759875735056736</v>
+        <v>3.763911662682641</v>
       </c>
       <c r="N3" t="n">
-        <v>22.37728680780519</v>
+        <v>22.43526445192404</v>
       </c>
       <c r="O3" t="n">
-        <v>4.730463699026259</v>
+        <v>4.736587849066461</v>
       </c>
       <c r="P3" t="n">
-        <v>340.3789742099627</v>
+        <v>340.4050986405674</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34251,28 +34315,28 @@
         <v>0.061</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08135319197191986</v>
+        <v>0.07889446336235534</v>
       </c>
       <c r="J4" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K4" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01659293147915086</v>
+        <v>0.01562514211738075</v>
       </c>
       <c r="M4" t="n">
-        <v>3.846905843245046</v>
+        <v>3.852221936989294</v>
       </c>
       <c r="N4" t="n">
-        <v>22.94710979671642</v>
+        <v>22.98987624286537</v>
       </c>
       <c r="O4" t="n">
-        <v>4.790314164719931</v>
+        <v>4.794775932498345</v>
       </c>
       <c r="P4" t="n">
-        <v>346.591135068369</v>
+        <v>346.6153617091895</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34329,28 +34393,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1772373163204592</v>
+        <v>0.1747549294926153</v>
       </c>
       <c r="J5" t="n">
+        <v>522</v>
+      </c>
+      <c r="K5" t="n">
         <v>521</v>
       </c>
-      <c r="K5" t="n">
-        <v>520</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.06985945314962427</v>
+        <v>0.06807774090166152</v>
       </c>
       <c r="M5" t="n">
-        <v>3.996203632759498</v>
+        <v>4.001077222372301</v>
       </c>
       <c r="N5" t="n">
-        <v>24.51292158560026</v>
+        <v>24.55448020765761</v>
       </c>
       <c r="O5" t="n">
-        <v>4.951052573503968</v>
+        <v>4.955247744326979</v>
       </c>
       <c r="P5" t="n">
-        <v>352.4753747943627</v>
+        <v>352.4998151181729</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34407,28 +34471,28 @@
         <v>0.0898</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2410463933539095</v>
+        <v>0.2376393940238523</v>
       </c>
       <c r="J6" t="n">
+        <v>522</v>
+      </c>
+      <c r="K6" t="n">
         <v>521</v>
       </c>
-      <c r="K6" t="n">
-        <v>520</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1075081156506815</v>
+        <v>0.1046359873926324</v>
       </c>
       <c r="M6" t="n">
-        <v>4.258527884763948</v>
+        <v>4.267810021650744</v>
       </c>
       <c r="N6" t="n">
-        <v>28.26998978110731</v>
+        <v>28.38263784106109</v>
       </c>
       <c r="O6" t="n">
-        <v>5.316953054250837</v>
+        <v>5.327535813212436</v>
       </c>
       <c r="P6" t="n">
-        <v>341.3534898593903</v>
+        <v>341.387033449742</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34485,28 +34549,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2965778313131496</v>
+        <v>0.2921322292474825</v>
       </c>
       <c r="J7" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K7" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1291869325764733</v>
+        <v>0.1253774963544496</v>
       </c>
       <c r="M7" t="n">
-        <v>4.781596048236738</v>
+        <v>4.795499795805661</v>
       </c>
       <c r="N7" t="n">
-        <v>34.81291052132439</v>
+        <v>35.03080447526695</v>
       </c>
       <c r="O7" t="n">
-        <v>5.900246649193946</v>
+        <v>5.918682663842263</v>
       </c>
       <c r="P7" t="n">
-        <v>340.5348577562294</v>
+        <v>340.5785917974935</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34563,28 +34627,28 @@
         <v>0.0935</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2483971575723548</v>
+        <v>0.2445843432726635</v>
       </c>
       <c r="J8" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K8" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08753080951628078</v>
+        <v>0.08497691539964314</v>
       </c>
       <c r="M8" t="n">
-        <v>5.011022336010711</v>
+        <v>5.021411523102812</v>
       </c>
       <c r="N8" t="n">
-        <v>37.76653323319172</v>
+        <v>37.9034293671936</v>
       </c>
       <c r="O8" t="n">
-        <v>6.145448171874182</v>
+        <v>6.156576107480001</v>
       </c>
       <c r="P8" t="n">
-        <v>345.9616168631097</v>
+        <v>345.9991257933855</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34641,28 +34705,28 @@
         <v>0.0954</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2895429194670339</v>
+        <v>0.2858073141183782</v>
       </c>
       <c r="J9" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K9" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1010262196594168</v>
+        <v>0.09864597147587184</v>
       </c>
       <c r="M9" t="n">
-        <v>5.424493099879927</v>
+        <v>5.43734454231449</v>
       </c>
       <c r="N9" t="n">
-        <v>43.8021505640483</v>
+        <v>43.9190399922605</v>
       </c>
       <c r="O9" t="n">
-        <v>6.618319315660759</v>
+        <v>6.627144180735809</v>
       </c>
       <c r="P9" t="n">
-        <v>342.3495652174913</v>
+        <v>342.3863145972268</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34719,28 +34783,28 @@
         <v>0.0872</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3548387593439128</v>
+        <v>0.3517723406837396</v>
       </c>
       <c r="J10" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K10" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1365188522113696</v>
+        <v>0.1346222876647156</v>
       </c>
       <c r="M10" t="n">
-        <v>5.708381104089968</v>
+        <v>5.715256989959807</v>
       </c>
       <c r="N10" t="n">
-        <v>46.76047871712523</v>
+        <v>46.8060753889976</v>
       </c>
       <c r="O10" t="n">
-        <v>6.838163402341687</v>
+        <v>6.841496575238315</v>
       </c>
       <c r="P10" t="n">
-        <v>341.6913191296745</v>
+        <v>341.7214853204931</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34797,28 +34861,28 @@
         <v>0.0772</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4017535849187599</v>
+        <v>0.398835962755694</v>
       </c>
       <c r="J11" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K11" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1504723356792298</v>
+        <v>0.1488436918061179</v>
       </c>
       <c r="M11" t="n">
-        <v>6.047917503694947</v>
+        <v>6.053377424024174</v>
       </c>
       <c r="N11" t="n">
-        <v>53.50532393388978</v>
+        <v>53.52511669931938</v>
       </c>
       <c r="O11" t="n">
-        <v>7.314733346738607</v>
+        <v>7.316086159916337</v>
       </c>
       <c r="P11" t="n">
-        <v>346.8306952479386</v>
+        <v>346.8593976387932</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34875,28 +34939,28 @@
         <v>0.0689</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4517127883716352</v>
+        <v>0.4478617538817386</v>
       </c>
       <c r="J12" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K12" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1741565308735059</v>
+        <v>0.1717528523062215</v>
       </c>
       <c r="M12" t="n">
-        <v>6.177851982059173</v>
+        <v>6.185525617815303</v>
       </c>
       <c r="N12" t="n">
-        <v>56.60454948100576</v>
+        <v>56.70886924521615</v>
       </c>
       <c r="O12" t="n">
-        <v>7.523599502964373</v>
+        <v>7.530529147756893</v>
       </c>
       <c r="P12" t="n">
-        <v>349.4470013900026</v>
+        <v>349.4849468667873</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34953,28 +35017,28 @@
         <v>0.0612</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4394723450134899</v>
+        <v>0.4351627099292385</v>
       </c>
       <c r="J13" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K13" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1112182954083689</v>
+        <v>0.1093945772199295</v>
       </c>
       <c r="M13" t="n">
-        <v>7.757334738028947</v>
+        <v>7.763727099980301</v>
       </c>
       <c r="N13" t="n">
-        <v>90.29226894491627</v>
+        <v>90.3857425100969</v>
       </c>
       <c r="O13" t="n">
-        <v>9.502224420887789</v>
+        <v>9.507141658253383</v>
       </c>
       <c r="P13" t="n">
-        <v>338.2319580729266</v>
+        <v>338.2744222883131</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35031,28 +35095,28 @@
         <v>0.0467</v>
       </c>
       <c r="I14" t="n">
-        <v>0.298925844318757</v>
+        <v>0.2932931198649647</v>
       </c>
       <c r="J14" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K14" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0327822608025935</v>
+        <v>0.03163159507563207</v>
       </c>
       <c r="M14" t="n">
-        <v>10.28813422060678</v>
+        <v>10.29519524361057</v>
       </c>
       <c r="N14" t="n">
-        <v>154.2342670258419</v>
+        <v>154.3939624220604</v>
       </c>
       <c r="O14" t="n">
-        <v>12.41910894653243</v>
+        <v>12.42553670559386</v>
       </c>
       <c r="P14" t="n">
-        <v>327.1335088229213</v>
+        <v>327.1890098618128</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35109,28 +35173,28 @@
         <v>0.0581</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2333250012088522</v>
+        <v>0.229813944803578</v>
       </c>
       <c r="J15" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K15" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05906609855801337</v>
+        <v>0.05743514817289197</v>
       </c>
       <c r="M15" t="n">
-        <v>5.882876757691345</v>
+        <v>5.88985556801729</v>
       </c>
       <c r="N15" t="n">
-        <v>50.7355037375285</v>
+        <v>50.81515961656045</v>
       </c>
       <c r="O15" t="n">
-        <v>7.12288591355558</v>
+        <v>7.128475265900868</v>
       </c>
       <c r="P15" t="n">
-        <v>333.7337924924901</v>
+        <v>333.7683880562705</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35168,7 +35232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P522"/>
+  <dimension ref="A1:P523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77927,6 +77991,88 @@
         </is>
       </c>
     </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>-34.98991690666662,173.70971564026695</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>-34.99066644339583,173.70970010393356</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>-34.9914085037782,173.70991167020082</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>-34.99213256618132,173.7102388078897</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>-34.99280570705264,173.71068945822984</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>-34.99340790217201,173.7112117497028</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>-34.99396690790622,173.71182958531438</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>-34.99449355659369,173.71248273511551</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>-34.99497780822303,173.71315470523075</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>-34.995452412803076,173.713846720435</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>-34.99593707463153,173.714537364917</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>-34.99644045198809,173.7152225466662</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>-34.99698541007348,173.7158728810235</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>-34.99728540666136,173.71670884920073</t>
+        </is>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0043/nzd0043.xlsx
+++ b/data/nzd0043/nzd0043.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P523"/>
+  <dimension ref="A1:P526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28674,6 +28674,168 @@
       <c r="P523" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>338.99</v>
+      </c>
+      <c r="C524" t="n">
+        <v>333.34</v>
+      </c>
+      <c r="D524" t="n">
+        <v>341.01</v>
+      </c>
+      <c r="E524" t="n">
+        <v>349.87</v>
+      </c>
+      <c r="F524" t="n">
+        <v>337.68</v>
+      </c>
+      <c r="G524" t="n">
+        <v>335.35</v>
+      </c>
+      <c r="H524" t="n">
+        <v>342.7</v>
+      </c>
+      <c r="I524" t="n">
+        <v>340.28</v>
+      </c>
+      <c r="J524" t="n">
+        <v>342.55</v>
+      </c>
+      <c r="K524" t="n">
+        <v>349.22</v>
+      </c>
+      <c r="L524" t="n">
+        <v>351.05</v>
+      </c>
+      <c r="M524" t="n">
+        <v>338.44</v>
+      </c>
+      <c r="N524" t="n">
+        <v>318.24</v>
+      </c>
+      <c r="O524" t="n">
+        <v>329.64</v>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>339.71</v>
+      </c>
+      <c r="C525" t="n">
+        <v>333.84</v>
+      </c>
+      <c r="D525" t="n">
+        <v>341.2</v>
+      </c>
+      <c r="E525" t="n">
+        <v>350.01</v>
+      </c>
+      <c r="F525" t="n">
+        <v>337.65</v>
+      </c>
+      <c r="G525" t="n">
+        <v>335.39</v>
+      </c>
+      <c r="H525" t="n">
+        <v>342.99</v>
+      </c>
+      <c r="I525" t="n">
+        <v>340.8</v>
+      </c>
+      <c r="J525" t="n">
+        <v>342.85</v>
+      </c>
+      <c r="K525" t="n">
+        <v>349.68</v>
+      </c>
+      <c r="L525" t="n">
+        <v>351.42</v>
+      </c>
+      <c r="M525" t="n">
+        <v>338.97</v>
+      </c>
+      <c r="N525" t="n">
+        <v>318.28</v>
+      </c>
+      <c r="O525" t="n">
+        <v>329.54</v>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>339.83</v>
+      </c>
+      <c r="C526" t="n">
+        <v>333.4</v>
+      </c>
+      <c r="D526" t="n">
+        <v>340.11</v>
+      </c>
+      <c r="E526" t="n">
+        <v>349.14</v>
+      </c>
+      <c r="F526" t="n">
+        <v>336.58</v>
+      </c>
+      <c r="G526" t="n">
+        <v>334.5</v>
+      </c>
+      <c r="H526" t="n">
+        <v>342.89</v>
+      </c>
+      <c r="I526" t="n">
+        <v>340.9</v>
+      </c>
+      <c r="J526" t="n">
+        <v>342.45</v>
+      </c>
+      <c r="K526" t="n">
+        <v>349.41</v>
+      </c>
+      <c r="L526" t="n">
+        <v>350.98</v>
+      </c>
+      <c r="M526" t="n">
+        <v>338.62</v>
+      </c>
+      <c r="N526" t="n">
+        <v>317.86</v>
+      </c>
+      <c r="O526" t="n">
+        <v>329.07</v>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28688,7 +28850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B530"/>
+  <dimension ref="A1:B533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33991,6 +34153,36 @@
       </c>
       <c r="B530" t="n">
         <v>0.41</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -34159,28 +34351,28 @@
         <v>0.0638</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.009007141853605471</v>
+        <v>-0.01616343941354691</v>
       </c>
       <c r="J2" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="K2" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001852873971764923</v>
+        <v>0.0005979179539391533</v>
       </c>
       <c r="M2" t="n">
-        <v>4.121536825644862</v>
+        <v>4.132702951108358</v>
       </c>
       <c r="N2" t="n">
-        <v>25.66579325092926</v>
+        <v>25.76700421426135</v>
       </c>
       <c r="O2" t="n">
-        <v>5.066141850652157</v>
+        <v>5.076120981050526</v>
       </c>
       <c r="P2" t="n">
-        <v>346.3849388299884</v>
+        <v>346.4556255687385</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34237,28 +34429,28 @@
         <v>0.0634</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.009400216871346161</v>
+        <v>-0.01655449496181492</v>
       </c>
       <c r="J3" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="K3" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002308613994312925</v>
+        <v>0.0007164560136336817</v>
       </c>
       <c r="M3" t="n">
-        <v>3.763911662682641</v>
+        <v>3.772767587767803</v>
       </c>
       <c r="N3" t="n">
-        <v>22.43526445192404</v>
+        <v>22.55427071672099</v>
       </c>
       <c r="O3" t="n">
-        <v>4.736587849066461</v>
+        <v>4.749133680653872</v>
       </c>
       <c r="P3" t="n">
-        <v>340.4050986405674</v>
+        <v>340.475767058903</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34315,28 +34507,28 @@
         <v>0.061</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07889446336235534</v>
+        <v>0.07035545461030217</v>
       </c>
       <c r="J4" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="K4" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01562514211738075</v>
+        <v>0.01242677964279804</v>
       </c>
       <c r="M4" t="n">
-        <v>3.852221936989294</v>
+        <v>3.874201222648732</v>
       </c>
       <c r="N4" t="n">
-        <v>22.98987624286537</v>
+        <v>23.21154070459968</v>
       </c>
       <c r="O4" t="n">
-        <v>4.794775932498345</v>
+        <v>4.817835686758078</v>
       </c>
       <c r="P4" t="n">
-        <v>346.6153617091895</v>
+        <v>346.6997100884294</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34393,28 +34585,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1747549294926153</v>
+        <v>0.1667463633253026</v>
       </c>
       <c r="J5" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="K5" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06807774090166152</v>
+        <v>0.0623317089789982</v>
       </c>
       <c r="M5" t="n">
-        <v>4.001077222372301</v>
+        <v>4.019183572675067</v>
       </c>
       <c r="N5" t="n">
-        <v>24.55448020765761</v>
+        <v>24.72484150407483</v>
       </c>
       <c r="O5" t="n">
-        <v>4.955247744326979</v>
+        <v>4.972408018664079</v>
       </c>
       <c r="P5" t="n">
-        <v>352.4998151181729</v>
+        <v>352.578861260717</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34471,28 +34663,28 @@
         <v>0.0898</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2376393940238523</v>
+        <v>0.2264938659568985</v>
       </c>
       <c r="J6" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="K6" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1046359873926324</v>
+        <v>0.09519617209826803</v>
       </c>
       <c r="M6" t="n">
-        <v>4.267810021650744</v>
+        <v>4.301198337624994</v>
       </c>
       <c r="N6" t="n">
-        <v>28.38263784106109</v>
+        <v>28.82228526183541</v>
       </c>
       <c r="O6" t="n">
-        <v>5.327535813212436</v>
+        <v>5.368639051178186</v>
       </c>
       <c r="P6" t="n">
-        <v>341.387033449742</v>
+        <v>341.4970420312709</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34549,28 +34741,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2921322292474825</v>
+        <v>0.2779169262390996</v>
       </c>
       <c r="J7" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="K7" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1253774963544496</v>
+        <v>0.1132620720777685</v>
       </c>
       <c r="M7" t="n">
-        <v>4.795499795805661</v>
+        <v>4.841641411323732</v>
       </c>
       <c r="N7" t="n">
-        <v>35.03080447526695</v>
+        <v>35.81019824036748</v>
       </c>
       <c r="O7" t="n">
-        <v>5.918682663842263</v>
+        <v>5.984162283926421</v>
       </c>
       <c r="P7" t="n">
-        <v>340.5785917974935</v>
+        <v>340.7187870417049</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34627,28 +34819,28 @@
         <v>0.0935</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2445843432726635</v>
+        <v>0.2342596246058237</v>
       </c>
       <c r="J8" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="K8" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08497691539964314</v>
+        <v>0.07839874391392487</v>
       </c>
       <c r="M8" t="n">
-        <v>5.021411523102812</v>
+        <v>5.046616509058296</v>
       </c>
       <c r="N8" t="n">
-        <v>37.9034293671936</v>
+        <v>38.20276411259196</v>
       </c>
       <c r="O8" t="n">
-        <v>6.156576107480001</v>
+        <v>6.180838463557509</v>
       </c>
       <c r="P8" t="n">
-        <v>345.9991257933855</v>
+        <v>346.1009493859792</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34705,28 +34897,28 @@
         <v>0.0954</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2858073141183782</v>
+        <v>0.2758388757055564</v>
       </c>
       <c r="J9" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="K9" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09864597147587184</v>
+        <v>0.09260814712902121</v>
       </c>
       <c r="M9" t="n">
-        <v>5.43734454231449</v>
+        <v>5.467657716749674</v>
       </c>
       <c r="N9" t="n">
-        <v>43.9190399922605</v>
+        <v>44.14917331960797</v>
       </c>
       <c r="O9" t="n">
-        <v>6.627144180735809</v>
+        <v>6.644484428426932</v>
       </c>
       <c r="P9" t="n">
-        <v>342.3863145972268</v>
+        <v>342.4846236984357</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34783,28 +34975,28 @@
         <v>0.0872</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3517723406837396</v>
+        <v>0.3427590640374716</v>
       </c>
       <c r="J10" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="K10" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1346222876647156</v>
+        <v>0.1291055595087531</v>
       </c>
       <c r="M10" t="n">
-        <v>5.715256989959807</v>
+        <v>5.734804094891559</v>
       </c>
       <c r="N10" t="n">
-        <v>46.8060753889976</v>
+        <v>46.9314981445195</v>
       </c>
       <c r="O10" t="n">
-        <v>6.841496575238315</v>
+        <v>6.850656767385117</v>
       </c>
       <c r="P10" t="n">
-        <v>341.7214853204931</v>
+        <v>341.8103759820615</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34861,28 +35053,28 @@
         <v>0.0772</v>
       </c>
       <c r="I11" t="n">
-        <v>0.398835962755694</v>
+        <v>0.3903011366829677</v>
       </c>
       <c r="J11" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="K11" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1488436918061179</v>
+        <v>0.1441261371772767</v>
       </c>
       <c r="M11" t="n">
-        <v>6.053377424024174</v>
+        <v>6.068132187674957</v>
       </c>
       <c r="N11" t="n">
-        <v>53.52511669931938</v>
+        <v>53.5713507089686</v>
       </c>
       <c r="O11" t="n">
-        <v>7.316086159916337</v>
+        <v>7.319245228093441</v>
       </c>
       <c r="P11" t="n">
-        <v>346.8593976387932</v>
+        <v>346.9435692314423</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34939,28 +35131,28 @@
         <v>0.0689</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4478617538817386</v>
+        <v>0.436947169172347</v>
       </c>
       <c r="J12" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="K12" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1717528523062215</v>
+        <v>0.1651237550582043</v>
       </c>
       <c r="M12" t="n">
-        <v>6.185525617815303</v>
+        <v>6.206164436583672</v>
       </c>
       <c r="N12" t="n">
-        <v>56.70886924521615</v>
+        <v>56.9597561704989</v>
       </c>
       <c r="O12" t="n">
-        <v>7.530529147756893</v>
+        <v>7.547168751955855</v>
       </c>
       <c r="P12" t="n">
-        <v>349.4849468667873</v>
+        <v>349.5927587894263</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35017,28 +35209,28 @@
         <v>0.0612</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4351627099292385</v>
+        <v>0.4232459444955572</v>
       </c>
       <c r="J13" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="K13" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1093945772199295</v>
+        <v>0.1045262729603578</v>
       </c>
       <c r="M13" t="n">
-        <v>7.763727099980301</v>
+        <v>7.778187273151413</v>
       </c>
       <c r="N13" t="n">
-        <v>90.3857425100969</v>
+        <v>90.554639825853</v>
       </c>
       <c r="O13" t="n">
-        <v>9.507141658253383</v>
+        <v>9.516020167373176</v>
       </c>
       <c r="P13" t="n">
-        <v>338.2744222883131</v>
+        <v>338.3921330574076</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35095,28 +35287,28 @@
         <v>0.0467</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2932931198649647</v>
+        <v>0.2751929345306652</v>
       </c>
       <c r="J14" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="K14" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03163159507563207</v>
+        <v>0.02800562945596352</v>
       </c>
       <c r="M14" t="n">
-        <v>10.29519524361057</v>
+        <v>10.32247516045071</v>
       </c>
       <c r="N14" t="n">
-        <v>154.3939624220604</v>
+        <v>155.0924596778922</v>
       </c>
       <c r="O14" t="n">
-        <v>12.42553670559386</v>
+        <v>12.45361231442075</v>
       </c>
       <c r="P14" t="n">
-        <v>327.1890098618128</v>
+        <v>327.367799668351</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35173,28 +35365,28 @@
         <v>0.0581</v>
       </c>
       <c r="I15" t="n">
-        <v>0.229813944803578</v>
+        <v>0.2185948412005299</v>
       </c>
       <c r="J15" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="K15" t="n">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05743514817289197</v>
+        <v>0.05226016594065952</v>
       </c>
       <c r="M15" t="n">
-        <v>5.88985556801729</v>
+        <v>5.914650356779225</v>
       </c>
       <c r="N15" t="n">
-        <v>50.81515961656045</v>
+        <v>51.13236505083442</v>
       </c>
       <c r="O15" t="n">
-        <v>7.128475265900868</v>
+        <v>7.150689830417371</v>
       </c>
       <c r="P15" t="n">
-        <v>333.7683880562705</v>
+        <v>333.8792086651599</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35232,7 +35424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P523"/>
+  <dimension ref="A1:P526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78073,6 +78265,252 @@
         </is>
       </c>
     </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>-34.98991625451435,173.70973797807616</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>-34.990666137097,173.70970469075323</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>-34.99141017851711,173.7099012385689</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>-34.99213430614409,173.7102344751331</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>-34.99280924665476,173.71068378154607</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>-34.993412149132816,173.7112050750957</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>-34.993962743182074,173.71183505378974</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>-34.99448972734488,173.7124870636996</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>-34.99497806853548,173.71315440185097</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>-34.99545340338197,173.7138456012956</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>-34.99593484536461,173.71453941422985</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>-34.99643666507857,173.71522551981604</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>-34.99699521377166,173.71586547917397</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>-34.99728989712505,173.71670559132195</t>
+        </is>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>-34.98991602434199,173.70974586200873</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>-34.990665772455316,173.7097101512528</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>-34.99140985047554,173.70990328187827</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>-34.99213375251959,173.7102358537375</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>-34.992809410021,173.71068351954528</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>-34.99341192851148,173.71120542182857</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>-34.99396096704964,173.71183738593345</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>-34.99448629422511,173.7124909444988</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>-34.99497611619206,173.71315667719938</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>-34.99545036560662,173.7138490333229</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>-34.99593218462663,173.71454186018374</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>-34.99643265095439,173.71522867135457</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>-34.9969949074061,173.71586571048178</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>-34.997290671342924,173.71670502961868</t>
+        </is>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>-34.989915985979884,173.70974717599748</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>-34.99066609334002,173.70970534601318</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>-34.99141173239778,173.70989155973473</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>-34.99213719290015,173.71022728669558</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>-34.99281523675003,173.71067417484934</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>-34.99341683733587,173.71119770702214</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>-34.99396157950911,173.71183658174598</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>-34.99448563400976,173.71249169080627</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>-34.99497871931662,173.71315364340148</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>-34.995452148648695,173.71384701887212</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>-34.99593534874747,173.71453895148179</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>-34.99643530179113,173.7152265901499</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>-34.99699812424447,173.71586328174956</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>-34.997294310166865,173.71670238961318</t>
+        </is>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0043/nzd0043.xlsx
+++ b/data/nzd0043/nzd0043.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P526"/>
+  <dimension ref="A1:P527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28834,6 +28834,60 @@
         <v>329.07</v>
       </c>
       <c r="P526" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>339.25</v>
+      </c>
+      <c r="C527" t="n">
+        <v>333.36</v>
+      </c>
+      <c r="D527" t="n">
+        <v>338.75</v>
+      </c>
+      <c r="E527" t="n">
+        <v>348.31</v>
+      </c>
+      <c r="F527" t="n">
+        <v>335.62</v>
+      </c>
+      <c r="G527" t="n">
+        <v>333.53</v>
+      </c>
+      <c r="H527" t="n">
+        <v>342.05</v>
+      </c>
+      <c r="I527" t="n">
+        <v>340.76</v>
+      </c>
+      <c r="J527" t="n">
+        <v>341.65</v>
+      </c>
+      <c r="K527" t="n">
+        <v>346.76</v>
+      </c>
+      <c r="L527" t="n">
+        <v>349.47</v>
+      </c>
+      <c r="M527" t="n">
+        <v>337.3</v>
+      </c>
+      <c r="N527" t="n">
+        <v>317.37</v>
+      </c>
+      <c r="O527" t="n">
+        <v>327.37</v>
+      </c>
+      <c r="P527" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28850,7 +28904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B533"/>
+  <dimension ref="A1:B534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34183,6 +34237,16 @@
       </c>
       <c r="B533" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -34351,28 +34415,28 @@
         <v>0.0638</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01616343941354691</v>
+        <v>-0.01860278014874665</v>
       </c>
       <c r="J2" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K2" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005979179539391533</v>
+        <v>0.0007923932948361578</v>
       </c>
       <c r="M2" t="n">
-        <v>4.132702951108358</v>
+        <v>4.13671530157661</v>
       </c>
       <c r="N2" t="n">
-        <v>25.76700421426135</v>
+        <v>25.80476567915801</v>
       </c>
       <c r="O2" t="n">
-        <v>5.076120981050526</v>
+        <v>5.079839139102538</v>
       </c>
       <c r="P2" t="n">
-        <v>346.4556255687385</v>
+        <v>346.4798153375382</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34429,28 +34493,28 @@
         <v>0.0634</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01655449496181492</v>
+        <v>-0.01895776611329462</v>
       </c>
       <c r="J3" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K3" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007164560136336817</v>
+        <v>0.0009396617712652544</v>
       </c>
       <c r="M3" t="n">
-        <v>3.772767587767803</v>
+        <v>3.775921919647999</v>
       </c>
       <c r="N3" t="n">
-        <v>22.55427071672099</v>
+        <v>22.59559358411051</v>
       </c>
       <c r="O3" t="n">
-        <v>4.749133680653872</v>
+        <v>4.753482258735223</v>
       </c>
       <c r="P3" t="n">
-        <v>340.475767058903</v>
+        <v>340.4995991429898</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34507,28 +34571,28 @@
         <v>0.061</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07035545461030217</v>
+        <v>0.06682616698104508</v>
       </c>
       <c r="J4" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K4" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01242677964279804</v>
+        <v>0.01118329706308108</v>
       </c>
       <c r="M4" t="n">
-        <v>3.874201222648732</v>
+        <v>3.885448670376153</v>
       </c>
       <c r="N4" t="n">
-        <v>23.21154070459968</v>
+        <v>23.34900127123758</v>
       </c>
       <c r="O4" t="n">
-        <v>4.817835686758078</v>
+        <v>4.832080428887497</v>
       </c>
       <c r="P4" t="n">
-        <v>346.6997100884294</v>
+        <v>346.7347083363362</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34585,28 +34649,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1667463633253026</v>
+        <v>0.1636265177200588</v>
       </c>
       <c r="J5" t="n">
+        <v>526</v>
+      </c>
+      <c r="K5" t="n">
         <v>525</v>
       </c>
-      <c r="K5" t="n">
-        <v>524</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.0623317089789982</v>
+        <v>0.06006396822514237</v>
       </c>
       <c r="M5" t="n">
-        <v>4.019183572675067</v>
+        <v>4.027935913016663</v>
       </c>
       <c r="N5" t="n">
-        <v>24.72484150407483</v>
+        <v>24.81997397512788</v>
       </c>
       <c r="O5" t="n">
-        <v>4.972408018664079</v>
+        <v>4.981964870924712</v>
       </c>
       <c r="P5" t="n">
-        <v>352.578861260717</v>
+        <v>352.6097753273746</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34663,28 +34727,28 @@
         <v>0.0898</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2264938659568985</v>
+        <v>0.2222244172709239</v>
       </c>
       <c r="J6" t="n">
+        <v>526</v>
+      </c>
+      <c r="K6" t="n">
         <v>525</v>
       </c>
-      <c r="K6" t="n">
-        <v>524</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.09519617209826803</v>
+        <v>0.09153715284721398</v>
       </c>
       <c r="M6" t="n">
-        <v>4.301198337624994</v>
+        <v>4.31553913665626</v>
       </c>
       <c r="N6" t="n">
-        <v>28.82228526183541</v>
+        <v>29.03374056740095</v>
       </c>
       <c r="O6" t="n">
-        <v>5.368639051178186</v>
+        <v>5.388296629492566</v>
       </c>
       <c r="P6" t="n">
-        <v>341.4970420312709</v>
+        <v>341.5393473367154</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34741,28 +34805,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2779169262390996</v>
+        <v>0.2726905362701333</v>
       </c>
       <c r="J7" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K7" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1132620720777685</v>
+        <v>0.1088151380332029</v>
       </c>
       <c r="M7" t="n">
-        <v>4.841641411323732</v>
+        <v>4.859528637239413</v>
       </c>
       <c r="N7" t="n">
-        <v>35.81019824036748</v>
+        <v>36.14191686869429</v>
       </c>
       <c r="O7" t="n">
-        <v>5.984162283926421</v>
+        <v>6.011814773318809</v>
       </c>
       <c r="P7" t="n">
-        <v>340.7187870417049</v>
+        <v>340.7705340592183</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34819,28 +34883,28 @@
         <v>0.0935</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2342596246058237</v>
+        <v>0.2305744765120164</v>
       </c>
       <c r="J8" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K8" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07839874391392487</v>
+        <v>0.07605640059469654</v>
       </c>
       <c r="M8" t="n">
-        <v>5.046616509058296</v>
+        <v>5.056230358704413</v>
       </c>
       <c r="N8" t="n">
-        <v>38.20276411259196</v>
+        <v>38.3287558782626</v>
       </c>
       <c r="O8" t="n">
-        <v>6.180838463557509</v>
+        <v>6.191022199787576</v>
       </c>
       <c r="P8" t="n">
-        <v>346.1009493859792</v>
+        <v>346.1374364112647</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34897,28 +34961,28 @@
         <v>0.0954</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2758388757055564</v>
+        <v>0.2725971775562047</v>
       </c>
       <c r="J9" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K9" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09260814712902121</v>
+        <v>0.09068631796574078</v>
       </c>
       <c r="M9" t="n">
-        <v>5.467657716749674</v>
+        <v>5.477077963404986</v>
       </c>
       <c r="N9" t="n">
-        <v>44.14917331960797</v>
+        <v>44.2188286069673</v>
       </c>
       <c r="O9" t="n">
-        <v>6.644484428426932</v>
+        <v>6.649723949681468</v>
       </c>
       <c r="P9" t="n">
-        <v>342.4846236984357</v>
+        <v>342.5167200808152</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34975,28 +35039,28 @@
         <v>0.0872</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3427590640374716</v>
+        <v>0.3394449995465044</v>
       </c>
       <c r="J10" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K10" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1291055595087531</v>
+        <v>0.1270046628716915</v>
       </c>
       <c r="M10" t="n">
-        <v>5.734804094891559</v>
+        <v>5.743081442539308</v>
       </c>
       <c r="N10" t="n">
-        <v>46.9314981445195</v>
+        <v>47.00279197368079</v>
       </c>
       <c r="O10" t="n">
-        <v>6.850656767385117</v>
+        <v>6.85585822298571</v>
       </c>
       <c r="P10" t="n">
-        <v>341.8103759820615</v>
+        <v>341.8431888709338</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35053,28 +35117,28 @@
         <v>0.0772</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3903011366829677</v>
+        <v>0.3865276976147531</v>
       </c>
       <c r="J11" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K11" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1441261371772767</v>
+        <v>0.1417642850790571</v>
       </c>
       <c r="M11" t="n">
-        <v>6.068132187674957</v>
+        <v>6.0782323320451</v>
       </c>
       <c r="N11" t="n">
-        <v>53.5713507089686</v>
+        <v>53.67765790536215</v>
       </c>
       <c r="O11" t="n">
-        <v>7.319245228093441</v>
+        <v>7.326503798222052</v>
       </c>
       <c r="P11" t="n">
-        <v>346.9435692314423</v>
+        <v>346.9809304346261</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35131,28 +35195,28 @@
         <v>0.0689</v>
       </c>
       <c r="I12" t="n">
-        <v>0.436947169172347</v>
+        <v>0.4327491902130416</v>
       </c>
       <c r="J12" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K12" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1651237550582043</v>
+        <v>0.16241646149446</v>
       </c>
       <c r="M12" t="n">
-        <v>6.206164436583672</v>
+        <v>6.215981816708792</v>
       </c>
       <c r="N12" t="n">
-        <v>56.9597561704989</v>
+        <v>57.10838645484527</v>
       </c>
       <c r="O12" t="n">
-        <v>7.547168751955855</v>
+        <v>7.557009094532391</v>
       </c>
       <c r="P12" t="n">
-        <v>349.5927587894263</v>
+        <v>349.6343881276268</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35209,28 +35273,28 @@
         <v>0.0612</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4232459444955572</v>
+        <v>0.4188301581874568</v>
       </c>
       <c r="J13" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K13" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1045262729603578</v>
+        <v>0.1026627298481045</v>
       </c>
       <c r="M13" t="n">
-        <v>7.778187273151413</v>
+        <v>7.785074344508181</v>
       </c>
       <c r="N13" t="n">
-        <v>90.554639825853</v>
+        <v>90.66675299577598</v>
       </c>
       <c r="O13" t="n">
-        <v>9.516020167373176</v>
+        <v>9.521909104574354</v>
       </c>
       <c r="P13" t="n">
-        <v>338.3921330574076</v>
+        <v>338.4359222863254</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35287,28 +35351,28 @@
         <v>0.0467</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2751929345306652</v>
+        <v>0.268979144012106</v>
       </c>
       <c r="J14" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K14" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02800562945596352</v>
+        <v>0.02679959002196142</v>
       </c>
       <c r="M14" t="n">
-        <v>10.32247516045071</v>
+        <v>10.33251782274906</v>
       </c>
       <c r="N14" t="n">
-        <v>155.0924596778922</v>
+        <v>155.3605036290448</v>
       </c>
       <c r="O14" t="n">
-        <v>12.45361231442075</v>
+        <v>12.46436936347142</v>
       </c>
       <c r="P14" t="n">
-        <v>327.367799668351</v>
+        <v>327.4294188402219</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35365,28 +35429,28 @@
         <v>0.0581</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2185948412005299</v>
+        <v>0.2141735883353312</v>
       </c>
       <c r="J15" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K15" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05226016594065952</v>
+        <v>0.05020019777195206</v>
       </c>
       <c r="M15" t="n">
-        <v>5.914650356779225</v>
+        <v>5.92645376572947</v>
       </c>
       <c r="N15" t="n">
-        <v>51.13236505083442</v>
+        <v>51.32012977607949</v>
       </c>
       <c r="O15" t="n">
-        <v>7.150689830417371</v>
+        <v>7.163806933194074</v>
       </c>
       <c r="P15" t="n">
-        <v>333.8792086651599</v>
+        <v>333.923052103295</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35424,7 +35488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P526"/>
+  <dimension ref="A1:P527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78511,6 +78575,88 @@
         </is>
       </c>
     </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>-34.98991617139661,173.70974082505182</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>-34.99066612251134,173.7097049091732</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>-34.99141408048265,173.70987693394022</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>-34.99214047510174,173.71021911353998</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>-34.99282046446894,173.71066579082196</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>-34.993422187402366,173.71118929874888</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>-34.99396672416839,173.71182982657066</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>-34.994486558311245,173.7124906459758</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>-34.994983925565485,173.71314757580512</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>-34.995469648874604,173.71382724740613</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>-34.99594620743434,173.7145289693438</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>-34.99644529923219,173.715218741034</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>-34.99700187722251,173.71586044822837</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>-34.99730747187005,173.7166928406551</t>
+        </is>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0043/nzd0043.xlsx
+++ b/data/nzd0043/nzd0043.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P527"/>
+  <dimension ref="A1:P529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28890,6 +28890,114 @@
       <c r="P527" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:26+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>341.48</v>
+      </c>
+      <c r="C528" t="n">
+        <v>335.79</v>
+      </c>
+      <c r="D528" t="n">
+        <v>340.38</v>
+      </c>
+      <c r="E528" t="n">
+        <v>350.17</v>
+      </c>
+      <c r="F528" t="n">
+        <v>336.61</v>
+      </c>
+      <c r="G528" t="n">
+        <v>333.85</v>
+      </c>
+      <c r="H528" t="n">
+        <v>342.88</v>
+      </c>
+      <c r="I528" t="n">
+        <v>343.78</v>
+      </c>
+      <c r="J528" t="n">
+        <v>344.65</v>
+      </c>
+      <c r="K528" t="n">
+        <v>349.87</v>
+      </c>
+      <c r="L528" t="n">
+        <v>353.57</v>
+      </c>
+      <c r="M528" t="n">
+        <v>342.71</v>
+      </c>
+      <c r="N528" t="n">
+        <v>323.45</v>
+      </c>
+      <c r="O528" t="n">
+        <v>330.79</v>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>341.45</v>
+      </c>
+      <c r="C529" t="n">
+        <v>336.54</v>
+      </c>
+      <c r="D529" t="n">
+        <v>340.93</v>
+      </c>
+      <c r="E529" t="n">
+        <v>351.02</v>
+      </c>
+      <c r="F529" t="n">
+        <v>337.77</v>
+      </c>
+      <c r="G529" t="n">
+        <v>335.41</v>
+      </c>
+      <c r="H529" t="n">
+        <v>344.15</v>
+      </c>
+      <c r="I529" t="n">
+        <v>344.88</v>
+      </c>
+      <c r="J529" t="n">
+        <v>345.81</v>
+      </c>
+      <c r="K529" t="n">
+        <v>351.04</v>
+      </c>
+      <c r="L529" t="n">
+        <v>355.11</v>
+      </c>
+      <c r="M529" t="n">
+        <v>344.46</v>
+      </c>
+      <c r="N529" t="n">
+        <v>325.82</v>
+      </c>
+      <c r="O529" t="n">
+        <v>332.98</v>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28904,7 +29012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B534"/>
+  <dimension ref="A1:B536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34247,6 +34355,26 @@
       </c>
       <c r="B534" t="n">
         <v>0.61</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -34415,28 +34543,28 @@
         <v>0.0638</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01860278014874665</v>
+        <v>-0.02185280432523415</v>
       </c>
       <c r="J2" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="K2" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007923932948361578</v>
+        <v>0.001098817439777133</v>
       </c>
       <c r="M2" t="n">
-        <v>4.13671530157661</v>
+        <v>4.136851020696316</v>
       </c>
       <c r="N2" t="n">
-        <v>25.80476567915801</v>
+        <v>25.78347525934371</v>
       </c>
       <c r="O2" t="n">
-        <v>5.079839139102538</v>
+        <v>5.077743126561614</v>
       </c>
       <c r="P2" t="n">
-        <v>346.4798153375382</v>
+        <v>346.5122248908252</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34493,28 +34621,28 @@
         <v>0.0634</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01895776611329462</v>
+        <v>-0.02171424988234075</v>
       </c>
       <c r="J3" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="K3" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009396617712652544</v>
+        <v>0.001239467811278927</v>
       </c>
       <c r="M3" t="n">
-        <v>3.775921919647999</v>
+        <v>3.773532967067077</v>
       </c>
       <c r="N3" t="n">
-        <v>22.59559358411051</v>
+        <v>22.56554870163174</v>
       </c>
       <c r="O3" t="n">
-        <v>4.753482258735223</v>
+        <v>4.750320905121225</v>
       </c>
       <c r="P3" t="n">
-        <v>340.4995991429898</v>
+        <v>340.5270858133463</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34571,28 +34699,28 @@
         <v>0.061</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06682616698104508</v>
+        <v>0.06118295195600033</v>
       </c>
       <c r="J4" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="K4" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01118329706308108</v>
+        <v>0.009375444830736823</v>
       </c>
       <c r="M4" t="n">
-        <v>3.885448670376153</v>
+        <v>3.900396944712448</v>
       </c>
       <c r="N4" t="n">
-        <v>23.34900127123758</v>
+        <v>23.49136087772098</v>
       </c>
       <c r="O4" t="n">
-        <v>4.832080428887497</v>
+        <v>4.846788718081384</v>
       </c>
       <c r="P4" t="n">
-        <v>346.7347083363362</v>
+        <v>346.7909820631759</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34649,28 +34777,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1636265177200588</v>
+        <v>0.1590610885871005</v>
       </c>
       <c r="J5" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="K5" t="n">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06006396822514237</v>
+        <v>0.05705697880699567</v>
       </c>
       <c r="M5" t="n">
-        <v>4.027935913016663</v>
+        <v>4.036590396736695</v>
       </c>
       <c r="N5" t="n">
-        <v>24.81997397512788</v>
+        <v>24.87769558005342</v>
       </c>
       <c r="O5" t="n">
-        <v>4.981964870924712</v>
+        <v>4.987754562932444</v>
       </c>
       <c r="P5" t="n">
-        <v>352.6097753273746</v>
+        <v>352.6552663709343</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34727,28 +34855,28 @@
         <v>0.0898</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2222244172709239</v>
+        <v>0.2148593104893641</v>
       </c>
       <c r="J6" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="K6" t="n">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09153715284721398</v>
+        <v>0.08566058944151034</v>
       </c>
       <c r="M6" t="n">
-        <v>4.31553913665626</v>
+        <v>4.338116054993217</v>
       </c>
       <c r="N6" t="n">
-        <v>29.03374056740095</v>
+        <v>29.31840271969092</v>
       </c>
       <c r="O6" t="n">
-        <v>5.388296629492566</v>
+        <v>5.414647054027706</v>
       </c>
       <c r="P6" t="n">
-        <v>341.5393473367154</v>
+        <v>341.6127353897993</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34805,28 +34933,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2726905362701333</v>
+        <v>0.2630800138952252</v>
       </c>
       <c r="J7" t="n">
+        <v>528</v>
+      </c>
+      <c r="K7" t="n">
         <v>526</v>
       </c>
-      <c r="K7" t="n">
-        <v>524</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1088151380332029</v>
+        <v>0.1011016988836392</v>
       </c>
       <c r="M7" t="n">
-        <v>4.859528637239413</v>
+        <v>4.890944148388257</v>
       </c>
       <c r="N7" t="n">
-        <v>36.14191686869429</v>
+        <v>36.67848108479659</v>
       </c>
       <c r="O7" t="n">
-        <v>6.011814773318809</v>
+        <v>6.056276173094865</v>
       </c>
       <c r="P7" t="n">
-        <v>340.7705340592183</v>
+        <v>340.8662228758198</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34883,28 +35011,28 @@
         <v>0.0935</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2305744765120164</v>
+        <v>0.2242928007880784</v>
       </c>
       <c r="J8" t="n">
+        <v>528</v>
+      </c>
+      <c r="K8" t="n">
         <v>526</v>
       </c>
-      <c r="K8" t="n">
-        <v>524</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.07605640059469654</v>
+        <v>0.07230683365828494</v>
       </c>
       <c r="M8" t="n">
-        <v>5.056230358704413</v>
+        <v>5.069819191967324</v>
       </c>
       <c r="N8" t="n">
-        <v>38.3287558782626</v>
+        <v>38.47150761267785</v>
       </c>
       <c r="O8" t="n">
-        <v>6.191022199787576</v>
+        <v>6.202540416045497</v>
       </c>
       <c r="P8" t="n">
-        <v>346.1374364112647</v>
+        <v>346.1999805938646</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34961,28 +35089,28 @@
         <v>0.0954</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2725971775562047</v>
+        <v>0.2687034747308061</v>
       </c>
       <c r="J9" t="n">
+        <v>528</v>
+      </c>
+      <c r="K9" t="n">
         <v>526</v>
       </c>
-      <c r="K9" t="n">
-        <v>524</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.09068631796574078</v>
+        <v>0.0887964755010302</v>
       </c>
       <c r="M9" t="n">
-        <v>5.477077963404986</v>
+        <v>5.479801838293174</v>
       </c>
       <c r="N9" t="n">
-        <v>44.2188286069673</v>
+        <v>44.16210356579769</v>
       </c>
       <c r="O9" t="n">
-        <v>6.649723949681468</v>
+        <v>6.64545736317657</v>
       </c>
       <c r="P9" t="n">
-        <v>342.5167200808152</v>
+        <v>342.5554876469641</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35039,28 +35167,28 @@
         <v>0.0872</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3394449995465044</v>
+        <v>0.335411876803879</v>
       </c>
       <c r="J10" t="n">
+        <v>528</v>
+      </c>
+      <c r="K10" t="n">
         <v>526</v>
       </c>
-      <c r="K10" t="n">
-        <v>524</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.1270046628716915</v>
+        <v>0.1249903712904925</v>
       </c>
       <c r="M10" t="n">
-        <v>5.743081442539308</v>
+        <v>5.744406896831975</v>
       </c>
       <c r="N10" t="n">
-        <v>47.00279197368079</v>
+        <v>46.94363024965546</v>
       </c>
       <c r="O10" t="n">
-        <v>6.85585822298571</v>
+        <v>6.851542180389424</v>
       </c>
       <c r="P10" t="n">
-        <v>341.8431888709338</v>
+        <v>341.8833445479889</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35117,28 +35245,28 @@
         <v>0.0772</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3865276976147531</v>
+        <v>0.3816590616602847</v>
       </c>
       <c r="J11" t="n">
+        <v>528</v>
+      </c>
+      <c r="K11" t="n">
         <v>526</v>
       </c>
-      <c r="K11" t="n">
-        <v>524</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1417642850790571</v>
+        <v>0.139296707318325</v>
       </c>
       <c r="M11" t="n">
-        <v>6.0782323320451</v>
+        <v>6.08301916963025</v>
       </c>
       <c r="N11" t="n">
-        <v>53.67765790536215</v>
+        <v>53.64722894499074</v>
       </c>
       <c r="O11" t="n">
-        <v>7.326503798222052</v>
+        <v>7.324426868021193</v>
       </c>
       <c r="P11" t="n">
-        <v>346.9809304346261</v>
+        <v>347.0294052424797</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35195,28 +35323,28 @@
         <v>0.0689</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4327491902130416</v>
+        <v>0.4278836048154957</v>
       </c>
       <c r="J12" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="K12" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L12" t="n">
-        <v>0.16241646149446</v>
+        <v>0.1600513170597569</v>
       </c>
       <c r="M12" t="n">
-        <v>6.215981816708792</v>
+        <v>6.21711222177047</v>
       </c>
       <c r="N12" t="n">
-        <v>57.10838645484527</v>
+        <v>57.06566852637088</v>
       </c>
       <c r="O12" t="n">
-        <v>7.557009094532391</v>
+        <v>7.554182187793122</v>
       </c>
       <c r="P12" t="n">
-        <v>349.6343881276268</v>
+        <v>349.682905686462</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35273,28 +35401,28 @@
         <v>0.0612</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4188301581874568</v>
+        <v>0.4145454373870823</v>
       </c>
       <c r="J13" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="K13" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1026627298481045</v>
+        <v>0.1013896287630497</v>
       </c>
       <c r="M13" t="n">
-        <v>7.785074344508181</v>
+        <v>7.776304340437405</v>
       </c>
       <c r="N13" t="n">
-        <v>90.66675299577598</v>
+        <v>90.45910554274417</v>
       </c>
       <c r="O13" t="n">
-        <v>9.521909104574354</v>
+        <v>9.510999187401088</v>
       </c>
       <c r="P13" t="n">
-        <v>338.4359222863254</v>
+        <v>338.478647073832</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35351,28 +35479,28 @@
         <v>0.0467</v>
       </c>
       <c r="I14" t="n">
-        <v>0.268979144012106</v>
+        <v>0.261844833072541</v>
       </c>
       <c r="J14" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="K14" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02679959002196142</v>
+        <v>0.02557562593734986</v>
       </c>
       <c r="M14" t="n">
-        <v>10.33251782274906</v>
+        <v>10.32707691571899</v>
       </c>
       <c r="N14" t="n">
-        <v>155.3605036290448</v>
+        <v>155.145791952497</v>
       </c>
       <c r="O14" t="n">
-        <v>12.46436936347142</v>
+        <v>12.45575336752045</v>
       </c>
       <c r="P14" t="n">
-        <v>327.4294188402219</v>
+        <v>327.5005589739965</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35429,28 +35557,28 @@
         <v>0.0581</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2141735883353312</v>
+        <v>0.2086239695332794</v>
       </c>
       <c r="J15" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="K15" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L15" t="n">
-        <v>0.05020019777195206</v>
+        <v>0.04792495945653508</v>
       </c>
       <c r="M15" t="n">
-        <v>5.92645376572947</v>
+        <v>5.93266969329728</v>
       </c>
       <c r="N15" t="n">
-        <v>51.32012977607949</v>
+        <v>51.35325202634596</v>
       </c>
       <c r="O15" t="n">
-        <v>7.163806933194074</v>
+        <v>7.166118337450615</v>
       </c>
       <c r="P15" t="n">
-        <v>333.923052103295</v>
+        <v>333.9783898359342</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35488,7 +35616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P527"/>
+  <dimension ref="A1:P529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78657,6 +78785,170 @@
         </is>
       </c>
     </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:26+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>-34.989915458499404,173.7097652433427</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>-34.990664350350386,173.7097314472006</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>-34.991411266233655,173.70989446338504</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>-34.992133119805864,173.71023742928534</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>-34.99281507338381,173.71067443685018</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>-34.99342042243204,173.71119207261233</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>-34.993961640755046,173.71183650132724</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>-34.994466619805685,173.71251318445712</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>-34.994964402130655,173.7131703292875</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>-34.99544911087331,173.71385045089932</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>-34.995916723580685,173.71455607315602</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>-34.9964043248683,173.71525091050464</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>-34.996955309653615,173.71589560700366</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>-34.99728099361938,173.71671205090882</t>
+        </is>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>-34.989915468089976,173.70976491484552</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>-34.99066380338596,173.70973963794955</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>-34.991410316639865,173.7099003782281</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>-34.99212975851381,173.7102457993829</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>-34.99280875655601,173.71068456754847</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>-34.99341181820082,173.711205595195</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>-34.99395386251947,173.7118467145074</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>-34.9944593574351,173.71252139383503</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>-34.994956853068054,173.71317912729776</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>-34.995441384357214,173.71385918018476</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>-34.99590564915605,173.7145662536073</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>-34.99639107068227,173.71526131651882</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>-34.99693715748998,173.7159093119761</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>-34.99726403824673,173.7167243522052</t>
+        </is>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0043/nzd0043.xlsx
+++ b/data/nzd0043/nzd0043.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P529"/>
+  <dimension ref="A1:P534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28998,6 +28998,276 @@
       <c r="P529" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:10+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>342.2</v>
+      </c>
+      <c r="C530" t="n">
+        <v>336.43</v>
+      </c>
+      <c r="D530" t="n">
+        <v>341.01</v>
+      </c>
+      <c r="E530" t="n">
+        <v>351.02</v>
+      </c>
+      <c r="F530" t="n">
+        <v>338.29</v>
+      </c>
+      <c r="G530" t="n">
+        <v>336.3</v>
+      </c>
+      <c r="H530" t="n">
+        <v>344.76</v>
+      </c>
+      <c r="I530" t="n">
+        <v>345.26</v>
+      </c>
+      <c r="J530" t="n">
+        <v>346.56</v>
+      </c>
+      <c r="K530" t="n">
+        <v>352.1</v>
+      </c>
+      <c r="L530" t="n">
+        <v>356.12</v>
+      </c>
+      <c r="M530" t="n">
+        <v>345.9</v>
+      </c>
+      <c r="N530" t="n">
+        <v>327.13</v>
+      </c>
+      <c r="O530" t="n">
+        <v>334.48</v>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>342.2</v>
+      </c>
+      <c r="C531" t="n">
+        <v>335.7</v>
+      </c>
+      <c r="D531" t="n">
+        <v>341.54</v>
+      </c>
+      <c r="E531" t="n">
+        <v>350.58</v>
+      </c>
+      <c r="F531" t="n">
+        <v>337.82</v>
+      </c>
+      <c r="G531" t="n">
+        <v>336.07</v>
+      </c>
+      <c r="H531" t="n">
+        <v>344.44</v>
+      </c>
+      <c r="I531" t="n">
+        <v>344.91</v>
+      </c>
+      <c r="J531" t="n">
+        <v>346.32</v>
+      </c>
+      <c r="K531" t="n">
+        <v>351.85</v>
+      </c>
+      <c r="L531" t="n">
+        <v>356.24</v>
+      </c>
+      <c r="M531" t="n">
+        <v>345.46</v>
+      </c>
+      <c r="N531" t="n">
+        <v>326.7</v>
+      </c>
+      <c r="O531" t="n">
+        <v>335.32</v>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>341.74</v>
+      </c>
+      <c r="C532" t="n">
+        <v>334.6</v>
+      </c>
+      <c r="D532" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="E532" t="n">
+        <v>349.07</v>
+      </c>
+      <c r="F532" t="n">
+        <v>335.83</v>
+      </c>
+      <c r="G532" t="n">
+        <v>336.28</v>
+      </c>
+      <c r="H532" t="n">
+        <v>344.68</v>
+      </c>
+      <c r="I532" t="n">
+        <v>345.06</v>
+      </c>
+      <c r="J532" t="n">
+        <v>345.72</v>
+      </c>
+      <c r="K532" t="n">
+        <v>351.89</v>
+      </c>
+      <c r="L532" t="n">
+        <v>355.17</v>
+      </c>
+      <c r="M532" t="n">
+        <v>344.31</v>
+      </c>
+      <c r="N532" t="n">
+        <v>326.11</v>
+      </c>
+      <c r="O532" t="n">
+        <v>334.34</v>
+      </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>341.64</v>
+      </c>
+      <c r="C533" t="n">
+        <v>334.04</v>
+      </c>
+      <c r="D533" t="n">
+        <v>338.99</v>
+      </c>
+      <c r="E533" t="n">
+        <v>348.61</v>
+      </c>
+      <c r="F533" t="n">
+        <v>335.56</v>
+      </c>
+      <c r="G533" t="n">
+        <v>336.06</v>
+      </c>
+      <c r="H533" t="n">
+        <v>344.48</v>
+      </c>
+      <c r="I533" t="n">
+        <v>344.3</v>
+      </c>
+      <c r="J533" t="n">
+        <v>345.14</v>
+      </c>
+      <c r="K533" t="n">
+        <v>351.13</v>
+      </c>
+      <c r="L533" t="n">
+        <v>353.7</v>
+      </c>
+      <c r="M533" t="n">
+        <v>343.43</v>
+      </c>
+      <c r="N533" t="n">
+        <v>325.84</v>
+      </c>
+      <c r="O533" t="n">
+        <v>333.96</v>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>342.01</v>
+      </c>
+      <c r="C534" t="n">
+        <v>333.52</v>
+      </c>
+      <c r="D534" t="n">
+        <v>339.29</v>
+      </c>
+      <c r="E534" t="n">
+        <v>349.04</v>
+      </c>
+      <c r="F534" t="n">
+        <v>335.26</v>
+      </c>
+      <c r="G534" t="n">
+        <v>336.31</v>
+      </c>
+      <c r="H534" t="n">
+        <v>344.02</v>
+      </c>
+      <c r="I534" t="n">
+        <v>343.85</v>
+      </c>
+      <c r="J534" t="n">
+        <v>344.2</v>
+      </c>
+      <c r="K534" t="n">
+        <v>350.35</v>
+      </c>
+      <c r="L534" t="n">
+        <v>352.54</v>
+      </c>
+      <c r="M534" t="n">
+        <v>341.81</v>
+      </c>
+      <c r="N534" t="n">
+        <v>325.78</v>
+      </c>
+      <c r="O534" t="n">
+        <v>333.13</v>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -29012,7 +29282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B536"/>
+  <dimension ref="A1:B541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34375,6 +34645,56 @@
       </c>
       <c r="B536" t="n">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -34543,28 +34863,28 @@
         <v>0.0638</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02185280432523415</v>
+        <v>-0.02886135478485648</v>
       </c>
       <c r="J2" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="K2" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001098817439777133</v>
+        <v>0.001943375709704598</v>
       </c>
       <c r="M2" t="n">
-        <v>4.136851020696316</v>
+        <v>4.131873250431452</v>
       </c>
       <c r="N2" t="n">
-        <v>25.78347525934371</v>
+        <v>25.6857698458886</v>
       </c>
       <c r="O2" t="n">
-        <v>5.077743126561614</v>
+        <v>5.068113045886862</v>
       </c>
       <c r="P2" t="n">
-        <v>346.5122248908252</v>
+        <v>346.5825224695824</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34621,28 +34941,28 @@
         <v>0.0634</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02171424988234075</v>
+        <v>-0.03070172016924647</v>
       </c>
       <c r="J3" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="K3" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001239467811278927</v>
+        <v>0.002497934516984102</v>
       </c>
       <c r="M3" t="n">
-        <v>3.773532967067077</v>
+        <v>3.776997086955923</v>
       </c>
       <c r="N3" t="n">
-        <v>22.56554870163174</v>
+        <v>22.60054545865738</v>
       </c>
       <c r="O3" t="n">
-        <v>4.750320905121225</v>
+        <v>4.754003098301196</v>
       </c>
       <c r="P3" t="n">
-        <v>340.5270858133463</v>
+        <v>340.6172547170646</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34699,28 +35019,28 @@
         <v>0.061</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06118295195600033</v>
+        <v>0.0465095516188776</v>
       </c>
       <c r="J4" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="K4" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009375444830736823</v>
+        <v>0.005402775888756928</v>
       </c>
       <c r="M4" t="n">
-        <v>3.900396944712448</v>
+        <v>3.94121471298518</v>
       </c>
       <c r="N4" t="n">
-        <v>23.49136087772098</v>
+        <v>23.90976697655766</v>
       </c>
       <c r="O4" t="n">
-        <v>4.846788718081384</v>
+        <v>4.889761443726847</v>
       </c>
       <c r="P4" t="n">
-        <v>346.7909820631759</v>
+        <v>346.9381744968787</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34777,28 +35097,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1590610885871005</v>
+        <v>0.1463070722612302</v>
       </c>
       <c r="J5" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="K5" t="n">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05705697880699567</v>
+        <v>0.04873909205969329</v>
       </c>
       <c r="M5" t="n">
-        <v>4.036590396736695</v>
+        <v>4.067013973112969</v>
       </c>
       <c r="N5" t="n">
-        <v>24.87769558005342</v>
+        <v>25.12908834191387</v>
       </c>
       <c r="O5" t="n">
-        <v>4.987754562932444</v>
+        <v>5.012892213275074</v>
       </c>
       <c r="P5" t="n">
-        <v>352.6552663709343</v>
+        <v>352.7831140181028</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34855,28 +35175,28 @@
         <v>0.0898</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2148593104893641</v>
+        <v>0.1958276972501589</v>
       </c>
       <c r="J6" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="K6" t="n">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08566058944151034</v>
+        <v>0.0711353074816522</v>
       </c>
       <c r="M6" t="n">
-        <v>4.338116054993217</v>
+        <v>4.399205874696214</v>
       </c>
       <c r="N6" t="n">
-        <v>29.31840271969092</v>
+        <v>30.11891719379332</v>
       </c>
       <c r="O6" t="n">
-        <v>5.414647054027706</v>
+        <v>5.488070443588832</v>
       </c>
       <c r="P6" t="n">
-        <v>341.6127353897993</v>
+        <v>341.8035076327233</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34933,28 +35253,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2630800138952252</v>
+        <v>0.2424996920722065</v>
       </c>
       <c r="J7" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="K7" t="n">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1011016988836392</v>
+        <v>0.08616793260864419</v>
       </c>
       <c r="M7" t="n">
-        <v>4.890944148388257</v>
+        <v>4.952767319083898</v>
       </c>
       <c r="N7" t="n">
-        <v>36.67848108479659</v>
+        <v>37.57790881364512</v>
       </c>
       <c r="O7" t="n">
-        <v>6.056276173094865</v>
+        <v>6.130082284410636</v>
       </c>
       <c r="P7" t="n">
-        <v>340.8662228758198</v>
+        <v>341.072330064315</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35011,28 +35331,28 @@
         <v>0.0935</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2242928007880784</v>
+        <v>0.2107137722349439</v>
       </c>
       <c r="J8" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="K8" t="n">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07230683365828494</v>
+        <v>0.06473532054298869</v>
       </c>
       <c r="M8" t="n">
-        <v>5.069819191967324</v>
+        <v>5.092689054357803</v>
       </c>
       <c r="N8" t="n">
-        <v>38.47150761267785</v>
+        <v>38.65169814702457</v>
       </c>
       <c r="O8" t="n">
-        <v>6.202540416045497</v>
+        <v>6.217048990238421</v>
       </c>
       <c r="P8" t="n">
-        <v>346.1999805938646</v>
+        <v>346.3359760658909</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35089,28 +35409,28 @@
         <v>0.0954</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2687034747308061</v>
+        <v>0.2598139550471596</v>
       </c>
       <c r="J9" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="K9" t="n">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0887964755010302</v>
+        <v>0.08465167737888135</v>
       </c>
       <c r="M9" t="n">
-        <v>5.479801838293174</v>
+        <v>5.481160095813927</v>
       </c>
       <c r="N9" t="n">
-        <v>44.16210356579769</v>
+        <v>43.98101771744851</v>
       </c>
       <c r="O9" t="n">
-        <v>6.64545736317657</v>
+        <v>6.631818582971681</v>
       </c>
       <c r="P9" t="n">
-        <v>342.5554876469641</v>
+        <v>342.644525450707</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35167,28 +35487,28 @@
         <v>0.0872</v>
       </c>
       <c r="I10" t="n">
-        <v>0.335411876803879</v>
+        <v>0.3261807179550003</v>
       </c>
       <c r="J10" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="K10" t="n">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1249903712904925</v>
+        <v>0.1205712343521068</v>
       </c>
       <c r="M10" t="n">
-        <v>5.744406896831975</v>
+        <v>5.743188405475244</v>
       </c>
       <c r="N10" t="n">
-        <v>46.94363024965546</v>
+        <v>46.75876514137235</v>
       </c>
       <c r="O10" t="n">
-        <v>6.851542180389424</v>
+        <v>6.838038106165565</v>
       </c>
       <c r="P10" t="n">
-        <v>341.8833445479889</v>
+        <v>341.9758136149662</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35245,28 +35565,28 @@
         <v>0.0772</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3816590616602847</v>
+        <v>0.3715489226571346</v>
       </c>
       <c r="J11" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="K11" t="n">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="L11" t="n">
-        <v>0.139296707318325</v>
+        <v>0.134673859536549</v>
       </c>
       <c r="M11" t="n">
-        <v>6.08301916963025</v>
+        <v>6.083073750973562</v>
       </c>
       <c r="N11" t="n">
-        <v>53.64722894499074</v>
+        <v>53.44634790094205</v>
       </c>
       <c r="O11" t="n">
-        <v>7.324426868021193</v>
+        <v>7.310700917213209</v>
       </c>
       <c r="P11" t="n">
-        <v>347.0294052424797</v>
+        <v>347.1306700646535</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35323,28 +35643,28 @@
         <v>0.0689</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4278836048154957</v>
+        <v>0.4167113105192602</v>
       </c>
       <c r="J12" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="K12" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1600513170597569</v>
+        <v>0.1548289987605354</v>
       </c>
       <c r="M12" t="n">
-        <v>6.21711222177047</v>
+        <v>6.215096676515152</v>
       </c>
       <c r="N12" t="n">
-        <v>57.06566852637088</v>
+        <v>56.91458944497113</v>
       </c>
       <c r="O12" t="n">
-        <v>7.554182187793122</v>
+        <v>7.54417586254265</v>
       </c>
       <c r="P12" t="n">
-        <v>349.682905686462</v>
+        <v>349.7949937949516</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35401,28 +35721,28 @@
         <v>0.0612</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4145454373870823</v>
+        <v>0.4051154579135509</v>
       </c>
       <c r="J13" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="K13" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1013896287630497</v>
+        <v>0.09879325248948212</v>
       </c>
       <c r="M13" t="n">
-        <v>7.776304340437405</v>
+        <v>7.748562519759246</v>
       </c>
       <c r="N13" t="n">
-        <v>90.45910554274417</v>
+        <v>89.89085870570692</v>
       </c>
       <c r="O13" t="n">
-        <v>9.510999187401088</v>
+        <v>9.481078984256323</v>
       </c>
       <c r="P13" t="n">
-        <v>338.478647073832</v>
+        <v>338.5732630350371</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35479,28 +35799,28 @@
         <v>0.0467</v>
       </c>
       <c r="I14" t="n">
-        <v>0.261844833072541</v>
+        <v>0.2474388610959275</v>
       </c>
       <c r="J14" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="K14" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02557562593734986</v>
+        <v>0.02327047379132052</v>
       </c>
       <c r="M14" t="n">
-        <v>10.32707691571899</v>
+        <v>10.29733902485774</v>
       </c>
       <c r="N14" t="n">
-        <v>155.145791952497</v>
+        <v>154.2999038135622</v>
       </c>
       <c r="O14" t="n">
-        <v>12.45575336752045</v>
+        <v>12.421751237791</v>
       </c>
       <c r="P14" t="n">
-        <v>327.5005589739965</v>
+        <v>327.6450595118889</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35557,28 +35877,28 @@
         <v>0.0581</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2086239695332794</v>
+        <v>0.199287138047967</v>
       </c>
       <c r="J15" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="K15" t="n">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04792495945653508</v>
+        <v>0.04455916181651753</v>
       </c>
       <c r="M15" t="n">
-        <v>5.93266969329728</v>
+        <v>5.924309851837617</v>
       </c>
       <c r="N15" t="n">
-        <v>51.35325202634596</v>
+        <v>51.13121073293243</v>
       </c>
       <c r="O15" t="n">
-        <v>7.166118337450615</v>
+        <v>7.150609116217473</v>
       </c>
       <c r="P15" t="n">
-        <v>333.9783898359342</v>
+        <v>334.0720495468586</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35616,7 +35936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P529"/>
+  <dimension ref="A1:P534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78949,6 +79269,416 @@
         </is>
       </c>
     </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:10+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>-34.98991522832527,173.7097731272751</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>-34.99066388360744,173.70973843663973</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>-34.99141017851711,173.7099012385689</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>-34.99212975851381,173.7102457993829</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>-34.99280592487432,173.71068910889545</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>-34.99340690937592,173.7112133100005</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>-34.99395012651625,173.7118516200499</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>-34.994456848616025,173.7125242298016</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>-34.994951972208284,173.7131848156656</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>-34.99543438426519,173.71386708876673</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>-34.995898386058926,173.71457293039532</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>-34.99638016437994,173.7152698791794</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>-34.99692712401492,173.71591688729583</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>-34.9972524249771,173.71673277774778</t>
+        </is>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>-34.98991522832527,173.7097731272751</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>-34.990664415986075,173.70973046431075</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>-34.991409263453704,173.7099069383266</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>-34.992131498476816,173.7102414666266</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>-34.99280848427894,173.71068500421643</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>-34.993408177948695,173.71121131628678</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>-34.993952086386805,173.7118490466506</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>-34.994459159370436,173.71252161772716</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>-34.994953534083436,173.71318299538797</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>-34.995436035230334,173.71386522353527</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>-34.99589752311667,173.71457372367698</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>-34.996383496861256,173.71526726281112</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>-34.99693041744572,173.7159144007407</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>-34.997245921545854,173.7167374960506</t>
+        </is>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>-34.98991537538103,173.7097680903183</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>-34.990665218199474,173.70971845121204</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>-34.99141244027649,173.70988715048796</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>-34.992137469712354,173.71022659739333</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>-34.99281932090547,173.71066762482806</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>-34.9934070196866,173.7112131366341</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>-34.99395061648389,173.7118509767001</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>-34.99445816904712,173.71252273718764</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>-34.994957438771216,173.71317844469357</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>-34.99543577107591,173.7138655219723</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>-34.99590521768495,173.71456665024823</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>-34.996392206755395,173.7152604245749</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>-34.99693493633905,173.71591098895544</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>-34.9972535088823,173.7167319913639</t>
+        </is>
+      </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>-34.98991540734964,173.7097669953277</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>-34.99066562659856,173.70971233545262</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>-34.99141366611486,173.70987951496284</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>-34.99213928876388,173.71022206769268</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>-34.99282079120135,173.71066526682023</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>-34.99340823310402,173.7112112296036</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>-34.993951841403,173.71184936832552</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>-34.9944631866851,173.71251706525416</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>-34.99496121330255,173.7131740456886</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>-34.9954407900098,173.7138598516682</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>-34.995915788726684,173.71455693254487</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>-34.99639887171758,173.71525519183658</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>-34.99693700430716,173.71590942762984</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>-34.99725645091064,173.7167298568933</t>
+        </is>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>-34.98991528906571,173.70977104679292</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>-34.99066600582602,173.7097066565331</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>-34.99141314815504,173.7098827412411</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>-34.99213758834616,173.71022630197808</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>-34.99282242486338,173.71066264681141</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>-34.99340685422058,173.7112133966837</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>-34.993954658716845,173.71184566906382</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>-34.994466157654855,173.71251370687213</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>-34.994967330646155,173.71316691626583</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>-34.995445941020634,173.71385403214484</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>-34.99592413050057,173.71454926415134</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>-34.9964111413065,173.71524555883892</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>-34.99693746385562,173.7159090806686</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>-34.9972628769198,173.71672519475956</t>
+        </is>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0043/nzd0043.xlsx
+++ b/data/nzd0043/nzd0043.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P534"/>
+  <dimension ref="A1:P537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29266,6 +29266,168 @@
         <v>333.13</v>
       </c>
       <c r="P534" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>341.5</v>
+      </c>
+      <c r="C535" t="n">
+        <v>332.92</v>
+      </c>
+      <c r="D535" t="n">
+        <v>338.74</v>
+      </c>
+      <c r="E535" t="n">
+        <v>348.85</v>
+      </c>
+      <c r="F535" t="n">
+        <v>335.16</v>
+      </c>
+      <c r="G535" t="n">
+        <v>336.01</v>
+      </c>
+      <c r="H535" t="n">
+        <v>343.74</v>
+      </c>
+      <c r="I535" t="n">
+        <v>343.22</v>
+      </c>
+      <c r="J535" t="n">
+        <v>343.9</v>
+      </c>
+      <c r="K535" t="n">
+        <v>349.62</v>
+      </c>
+      <c r="L535" t="n">
+        <v>351.74</v>
+      </c>
+      <c r="M535" t="n">
+        <v>341.52</v>
+      </c>
+      <c r="N535" t="n">
+        <v>325.6</v>
+      </c>
+      <c r="O535" t="n">
+        <v>333.07</v>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>341.11</v>
+      </c>
+      <c r="C536" t="n">
+        <v>332.38</v>
+      </c>
+      <c r="D536" t="n">
+        <v>339.16</v>
+      </c>
+      <c r="E536" t="n">
+        <v>348.67</v>
+      </c>
+      <c r="F536" t="n">
+        <v>335.06</v>
+      </c>
+      <c r="G536" t="n">
+        <v>336.25</v>
+      </c>
+      <c r="H536" t="n">
+        <v>344.41</v>
+      </c>
+      <c r="I536" t="n">
+        <v>343.42</v>
+      </c>
+      <c r="J536" t="n">
+        <v>344.01</v>
+      </c>
+      <c r="K536" t="n">
+        <v>350</v>
+      </c>
+      <c r="L536" t="n">
+        <v>352.01</v>
+      </c>
+      <c r="M536" t="n">
+        <v>341.66</v>
+      </c>
+      <c r="N536" t="n">
+        <v>326.63</v>
+      </c>
+      <c r="O536" t="n">
+        <v>332.76</v>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>340.4</v>
+      </c>
+      <c r="C537" t="n">
+        <v>331.76</v>
+      </c>
+      <c r="D537" t="n">
+        <v>338.6</v>
+      </c>
+      <c r="E537" t="n">
+        <v>348.03</v>
+      </c>
+      <c r="F537" t="n">
+        <v>335.01</v>
+      </c>
+      <c r="G537" t="n">
+        <v>336.2</v>
+      </c>
+      <c r="H537" t="n">
+        <v>344.16</v>
+      </c>
+      <c r="I537" t="n">
+        <v>342.68</v>
+      </c>
+      <c r="J537" t="n">
+        <v>342.99</v>
+      </c>
+      <c r="K537" t="n">
+        <v>349.21</v>
+      </c>
+      <c r="L537" t="n">
+        <v>351.28</v>
+      </c>
+      <c r="M537" t="n">
+        <v>340.52</v>
+      </c>
+      <c r="N537" t="n">
+        <v>325.63</v>
+      </c>
+      <c r="O537" t="n">
+        <v>331.32</v>
+      </c>
+      <c r="P537" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29282,7 +29444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B541"/>
+  <dimension ref="A1:B544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34695,6 +34857,36 @@
       </c>
       <c r="B541" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -34863,28 +35055,28 @@
         <v>0.0638</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02886135478485648</v>
+        <v>-0.03389824980292247</v>
       </c>
       <c r="J2" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="K2" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001943375709704598</v>
+        <v>0.002697638819925907</v>
       </c>
       <c r="M2" t="n">
-        <v>4.131873250431452</v>
+        <v>4.13309684543959</v>
       </c>
       <c r="N2" t="n">
-        <v>25.6857698458886</v>
+        <v>25.67019346054326</v>
       </c>
       <c r="O2" t="n">
-        <v>5.068113045886862</v>
+        <v>5.066576108235547</v>
       </c>
       <c r="P2" t="n">
-        <v>346.5825224695824</v>
+        <v>346.6332425819468</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34941,28 +35133,28 @@
         <v>0.0634</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03070172016924647</v>
+        <v>-0.03850092671103316</v>
       </c>
       <c r="J3" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="K3" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002497934516984102</v>
+        <v>0.00391667661574524</v>
       </c>
       <c r="M3" t="n">
-        <v>3.776997086955923</v>
+        <v>3.789174903960647</v>
       </c>
       <c r="N3" t="n">
-        <v>22.60054545865738</v>
+        <v>22.77990274687458</v>
       </c>
       <c r="O3" t="n">
-        <v>4.754003098301196</v>
+        <v>4.772829637319415</v>
       </c>
       <c r="P3" t="n">
-        <v>340.6172547170646</v>
+        <v>340.6957884814613</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35019,28 +35211,28 @@
         <v>0.061</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0465095516188776</v>
+        <v>0.03671619961064512</v>
       </c>
       <c r="J4" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="K4" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005402775888756928</v>
+        <v>0.003347038373979427</v>
       </c>
       <c r="M4" t="n">
-        <v>3.94121471298518</v>
+        <v>3.972962084217232</v>
       </c>
       <c r="N4" t="n">
-        <v>23.90976697655766</v>
+        <v>24.2566186277361</v>
       </c>
       <c r="O4" t="n">
-        <v>4.889761443726847</v>
+        <v>4.925100874879224</v>
       </c>
       <c r="P4" t="n">
-        <v>346.9381744968787</v>
+        <v>347.0367831046805</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35097,28 +35289,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1463070722612302</v>
+        <v>0.1377408482782053</v>
       </c>
       <c r="J5" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="K5" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04873909205969329</v>
+        <v>0.04332859609083262</v>
       </c>
       <c r="M5" t="n">
-        <v>4.067013973112969</v>
+        <v>4.092005495416056</v>
       </c>
       <c r="N5" t="n">
-        <v>25.12908834191387</v>
+        <v>25.35718265205278</v>
       </c>
       <c r="O5" t="n">
-        <v>5.012892213275074</v>
+        <v>5.035591589083927</v>
       </c>
       <c r="P5" t="n">
-        <v>352.7831140181028</v>
+        <v>352.8693068588681</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35175,28 +35367,28 @@
         <v>0.0898</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1958276972501589</v>
+        <v>0.1833006251041584</v>
       </c>
       <c r="J6" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="K6" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0711353074816522</v>
+        <v>0.06206076526108151</v>
       </c>
       <c r="M6" t="n">
-        <v>4.399205874696214</v>
+        <v>4.443172010280116</v>
       </c>
       <c r="N6" t="n">
-        <v>30.11891719379332</v>
+        <v>30.73780039373132</v>
       </c>
       <c r="O6" t="n">
-        <v>5.488070443588832</v>
+        <v>5.544168142628011</v>
       </c>
       <c r="P6" t="n">
-        <v>341.8035076327233</v>
+        <v>341.9295503466949</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35253,28 +35445,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2424996920722065</v>
+        <v>0.2305594395870928</v>
       </c>
       <c r="J7" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="K7" t="n">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08616793260864419</v>
+        <v>0.07803361222698657</v>
       </c>
       <c r="M7" t="n">
-        <v>4.952767319083898</v>
+        <v>4.989899179156445</v>
       </c>
       <c r="N7" t="n">
-        <v>37.57790881364512</v>
+        <v>38.08419451468809</v>
       </c>
       <c r="O7" t="n">
-        <v>6.130082284410636</v>
+        <v>6.171239301363065</v>
       </c>
       <c r="P7" t="n">
-        <v>341.072330064315</v>
+        <v>341.1923790784472</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35331,28 +35523,28 @@
         <v>0.0935</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2107137722349439</v>
+        <v>0.202478413952566</v>
       </c>
       <c r="J8" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="K8" t="n">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06473532054298869</v>
+        <v>0.06024905266463099</v>
       </c>
       <c r="M8" t="n">
-        <v>5.092689054357803</v>
+        <v>5.106523504707443</v>
       </c>
       <c r="N8" t="n">
-        <v>38.65169814702457</v>
+        <v>38.7762308273831</v>
       </c>
       <c r="O8" t="n">
-        <v>6.217048990238421</v>
+        <v>6.227056353316798</v>
       </c>
       <c r="P8" t="n">
-        <v>346.3359760658909</v>
+        <v>346.4187744054381</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35409,28 +35601,28 @@
         <v>0.0954</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2598139550471596</v>
+        <v>0.2530226274233081</v>
       </c>
       <c r="J9" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="K9" t="n">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08465167737888135</v>
+        <v>0.08113254362682321</v>
       </c>
       <c r="M9" t="n">
-        <v>5.481160095813927</v>
+        <v>5.490386797860821</v>
       </c>
       <c r="N9" t="n">
-        <v>43.98101771744851</v>
+        <v>43.96651904593437</v>
       </c>
       <c r="O9" t="n">
-        <v>6.631818582971681</v>
+        <v>6.630725378564126</v>
       </c>
       <c r="P9" t="n">
-        <v>342.644525450707</v>
+        <v>342.71280887266</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35487,28 +35679,28 @@
         <v>0.0872</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3261807179550003</v>
+        <v>0.3187868759093856</v>
       </c>
       <c r="J10" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="K10" t="n">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1205712343521068</v>
+        <v>0.1164143194256478</v>
       </c>
       <c r="M10" t="n">
-        <v>5.743188405475244</v>
+        <v>5.752887343112115</v>
       </c>
       <c r="N10" t="n">
-        <v>46.75876514137235</v>
+        <v>46.77229872505183</v>
       </c>
       <c r="O10" t="n">
-        <v>6.838038106165565</v>
+        <v>6.839027615461998</v>
       </c>
       <c r="P10" t="n">
-        <v>341.9758136149662</v>
+        <v>342.0501563015303</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35565,28 +35757,28 @@
         <v>0.0772</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3715489226571346</v>
+        <v>0.3637457810543621</v>
       </c>
       <c r="J11" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="K11" t="n">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="L11" t="n">
-        <v>0.134673859536549</v>
+        <v>0.1305073963665349</v>
       </c>
       <c r="M11" t="n">
-        <v>6.083073750973562</v>
+        <v>6.09283159301241</v>
       </c>
       <c r="N11" t="n">
-        <v>53.44634790094205</v>
+        <v>53.45302380058988</v>
       </c>
       <c r="O11" t="n">
-        <v>7.310700917213209</v>
+        <v>7.311157487059753</v>
       </c>
       <c r="P11" t="n">
-        <v>347.1306700646535</v>
+        <v>347.2091259772309</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35643,28 +35835,28 @@
         <v>0.0689</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4167113105192602</v>
+        <v>0.407013225727138</v>
       </c>
       <c r="J12" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="K12" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1548289987605354</v>
+        <v>0.1492344058012879</v>
       </c>
       <c r="M12" t="n">
-        <v>6.215096676515152</v>
+        <v>6.229217122551582</v>
       </c>
       <c r="N12" t="n">
-        <v>56.91458944497113</v>
+        <v>57.06759184503418</v>
       </c>
       <c r="O12" t="n">
-        <v>7.54417586254265</v>
+        <v>7.554309488300977</v>
       </c>
       <c r="P12" t="n">
-        <v>349.7949937949516</v>
+        <v>349.8926444493769</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35721,28 +35913,28 @@
         <v>0.0612</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4051154579135509</v>
+        <v>0.3965586845535288</v>
       </c>
       <c r="J13" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="K13" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09879325248948212</v>
+        <v>0.09573672466529493</v>
       </c>
       <c r="M13" t="n">
-        <v>7.748562519759246</v>
+        <v>7.746848510865068</v>
       </c>
       <c r="N13" t="n">
-        <v>89.89085870570692</v>
+        <v>89.75585824684458</v>
       </c>
       <c r="O13" t="n">
-        <v>9.481078984256323</v>
+        <v>9.473956842145977</v>
       </c>
       <c r="P13" t="n">
-        <v>338.5732630350371</v>
+        <v>338.6594240061459</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35799,28 +35991,28 @@
         <v>0.0467</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2474388610959275</v>
+        <v>0.2387356079270548</v>
       </c>
       <c r="J14" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="K14" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02327047379132052</v>
+        <v>0.02190004501990139</v>
       </c>
       <c r="M14" t="n">
-        <v>10.29733902485774</v>
+        <v>10.27980259711617</v>
       </c>
       <c r="N14" t="n">
-        <v>154.2999038135622</v>
+        <v>153.8169432084899</v>
       </c>
       <c r="O14" t="n">
-        <v>12.421751237791</v>
+        <v>12.40229588457274</v>
       </c>
       <c r="P14" t="n">
-        <v>327.6450595118889</v>
+        <v>327.7326913265157</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35877,28 +36069,28 @@
         <v>0.0581</v>
       </c>
       <c r="I15" t="n">
-        <v>0.199287138047967</v>
+        <v>0.1919368034726161</v>
       </c>
       <c r="J15" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="K15" t="n">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04455916181651753</v>
+        <v>0.04173062625193757</v>
       </c>
       <c r="M15" t="n">
-        <v>5.924309851837617</v>
+        <v>5.928109344330484</v>
       </c>
       <c r="N15" t="n">
-        <v>51.13121073293243</v>
+        <v>51.11881375267468</v>
       </c>
       <c r="O15" t="n">
-        <v>7.150609116217473</v>
+        <v>7.14974221581972</v>
       </c>
       <c r="P15" t="n">
-        <v>334.0720495468586</v>
+        <v>334.1460658806752</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35936,7 +36128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P534"/>
+  <dimension ref="A1:P537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79679,6 +79871,252 @@
         </is>
       </c>
     </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>-34.98991545210569,173.7097654623408</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>-34.99066644339583,173.70970010393356</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>-34.99141409774798,173.7098768263976</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>-34.99213833969355,173.71022443101478</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>-34.99282296941738,173.71066177347515</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>-34.99340850888072,173.71121079618754</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>-34.993956373603496,173.7118434173392</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>-34.994470317012336,173.7125090051369</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>-34.994969282989764,173.7131646409179</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>-34.99545076183821,173.71384858566717</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>-34.9959298834478,173.7145439756032</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>-34.996413337714316,173.71524383441312</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>-34.99693884250101,173.7159080397848</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>-34.99726334145058,173.71672485773786</t>
+        </is>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>-34.98991557678313,173.70976119187742</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>-34.99066683720836,173.70969420659392</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>-34.991413372604306,173.7098813431872</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>-34.9921390514963,173.7102226585232</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>-34.992823513971366,173.71066090013883</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>-34.99340718515262,173.71121287658448</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>-34.99395227012468,173.71184880539442</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>-34.9944689965814,173.7125104977513</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>-34.99496856713045,173.71316547521215</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>-34.99544825237155,173.71385142082</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>-34.99592794182814,173.7145457604883</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>-34.99641227737952,173.71524466689453</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>-34.996930953585604,173.71591399595263</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>-34.997265741526235,173.71672311645878</t>
+        </is>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>-34.98991580375965,173.70975341744403</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>-34.99066728936313,173.70968743557427</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>-34.991414339462494,173.70987532080105</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>-34.99214158235034,173.71021635633073</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>-34.99282378624836,173.71066046347067</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>-34.993407460929305,173.71121244316845</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>-34.993953801273506,173.71184679492612</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>-34.994473882175754,173.71250497507776</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>-34.994975205098456,173.7131577390286</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>-34.99545346942057,173.71384552668633</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>-34.99593319139236,173.7145409346877</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>-34.99642091153419,173.7152378881165</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>-34.99693861272679,173.71590821326544</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>-34.997276890264466,173.71671502793538</t>
+        </is>
+      </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0043/nzd0043.xlsx
+++ b/data/nzd0043/nzd0043.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P537"/>
+  <dimension ref="A1:P540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29428,6 +29428,168 @@
         <v>331.32</v>
       </c>
       <c r="P537" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>339.92</v>
+      </c>
+      <c r="C538" t="n">
+        <v>331.44</v>
+      </c>
+      <c r="D538" t="n">
+        <v>338.09</v>
+      </c>
+      <c r="E538" t="n">
+        <v>347.75</v>
+      </c>
+      <c r="F538" t="n">
+        <v>335.29</v>
+      </c>
+      <c r="G538" t="n">
+        <v>336.88</v>
+      </c>
+      <c r="H538" t="n">
+        <v>344.03</v>
+      </c>
+      <c r="I538" t="n">
+        <v>342.14</v>
+      </c>
+      <c r="J538" t="n">
+        <v>342.67</v>
+      </c>
+      <c r="K538" t="n">
+        <v>347.92</v>
+      </c>
+      <c r="L538" t="n">
+        <v>350.73</v>
+      </c>
+      <c r="M538" t="n">
+        <v>339.86</v>
+      </c>
+      <c r="N538" t="n">
+        <v>327.97</v>
+      </c>
+      <c r="O538" t="n">
+        <v>332.77</v>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>341.08</v>
+      </c>
+      <c r="C539" t="n">
+        <v>332.36</v>
+      </c>
+      <c r="D539" t="n">
+        <v>338.7</v>
+      </c>
+      <c r="E539" t="n">
+        <v>347.97</v>
+      </c>
+      <c r="F539" t="n">
+        <v>335.91</v>
+      </c>
+      <c r="G539" t="n">
+        <v>337.19</v>
+      </c>
+      <c r="H539" t="n">
+        <v>344.41</v>
+      </c>
+      <c r="I539" t="n">
+        <v>342.44</v>
+      </c>
+      <c r="J539" t="n">
+        <v>343.04</v>
+      </c>
+      <c r="K539" t="n">
+        <v>347.9</v>
+      </c>
+      <c r="L539" t="n">
+        <v>351.39</v>
+      </c>
+      <c r="M539" t="n">
+        <v>340.93</v>
+      </c>
+      <c r="N539" t="n">
+        <v>328.51</v>
+      </c>
+      <c r="O539" t="n">
+        <v>333.45</v>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>341.81</v>
+      </c>
+      <c r="C540" t="n">
+        <v>333.18</v>
+      </c>
+      <c r="D540" t="n">
+        <v>339.72</v>
+      </c>
+      <c r="E540" t="n">
+        <v>348.23</v>
+      </c>
+      <c r="F540" t="n">
+        <v>336.59</v>
+      </c>
+      <c r="G540" t="n">
+        <v>337.27</v>
+      </c>
+      <c r="H540" t="n">
+        <v>343.81</v>
+      </c>
+      <c r="I540" t="n">
+        <v>341.91</v>
+      </c>
+      <c r="J540" t="n">
+        <v>342.66</v>
+      </c>
+      <c r="K540" t="n">
+        <v>347.35</v>
+      </c>
+      <c r="L540" t="n">
+        <v>351.88</v>
+      </c>
+      <c r="M540" t="n">
+        <v>341.13</v>
+      </c>
+      <c r="N540" t="n">
+        <v>329.64</v>
+      </c>
+      <c r="O540" t="n">
+        <v>334.16</v>
+      </c>
+      <c r="P540" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29444,7 +29606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B544"/>
+  <dimension ref="A1:B547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34887,6 +35049,36 @@
       </c>
       <c r="B544" t="n">
         <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -35055,28 +35247,28 @@
         <v>0.0638</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03389824980292247</v>
+        <v>-0.03886741361379183</v>
       </c>
       <c r="J2" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K2" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002697638819925907</v>
+        <v>0.003567902085048424</v>
       </c>
       <c r="M2" t="n">
-        <v>4.13309684543959</v>
+        <v>4.134677755978825</v>
       </c>
       <c r="N2" t="n">
-        <v>25.67019346054326</v>
+        <v>25.65597802425262</v>
       </c>
       <c r="O2" t="n">
-        <v>5.066576108235547</v>
+        <v>5.065173049783454</v>
       </c>
       <c r="P2" t="n">
-        <v>346.6332425819468</v>
+        <v>346.683493774493</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35133,28 +35325,28 @@
         <v>0.0634</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03850092671103316</v>
+        <v>-0.04611812397290446</v>
       </c>
       <c r="J3" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K3" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00391667661574524</v>
+        <v>0.005603971237536864</v>
       </c>
       <c r="M3" t="n">
-        <v>3.789174903960647</v>
+        <v>3.8004530738589</v>
       </c>
       <c r="N3" t="n">
-        <v>22.77990274687458</v>
+        <v>22.95034708613656</v>
       </c>
       <c r="O3" t="n">
-        <v>4.772829637319415</v>
+        <v>4.790652052292732</v>
       </c>
       <c r="P3" t="n">
-        <v>340.6957884814613</v>
+        <v>340.7728202008457</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35211,28 +35403,28 @@
         <v>0.061</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03671619961064512</v>
+        <v>0.02718046278127911</v>
       </c>
       <c r="J4" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K4" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003347038373979427</v>
+        <v>0.001824000162243045</v>
       </c>
       <c r="M4" t="n">
-        <v>3.972962084217232</v>
+        <v>4.003895416780034</v>
       </c>
       <c r="N4" t="n">
-        <v>24.2566186277361</v>
+        <v>24.58546654043382</v>
       </c>
       <c r="O4" t="n">
-        <v>4.925100874879224</v>
+        <v>4.958373376464687</v>
       </c>
       <c r="P4" t="n">
-        <v>347.0367831046805</v>
+        <v>347.1332176137396</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35289,28 +35481,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1377408482782053</v>
+        <v>0.1288351764568476</v>
       </c>
       <c r="J5" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K5" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04332859609083262</v>
+        <v>0.0379683985197482</v>
       </c>
       <c r="M5" t="n">
-        <v>4.092005495416056</v>
+        <v>4.119818518340225</v>
       </c>
       <c r="N5" t="n">
-        <v>25.35718265205278</v>
+        <v>25.61927987591532</v>
       </c>
       <c r="O5" t="n">
-        <v>5.035591589083927</v>
+        <v>5.061549157710051</v>
       </c>
       <c r="P5" t="n">
-        <v>352.8693068588681</v>
+        <v>352.9593077080427</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35367,28 +35559,28 @@
         <v>0.0898</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1833006251041584</v>
+        <v>0.1719671466884463</v>
       </c>
       <c r="J6" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K6" t="n">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06206076526108151</v>
+        <v>0.0545520470488623</v>
       </c>
       <c r="M6" t="n">
-        <v>4.443172010280116</v>
+        <v>4.481794057705518</v>
       </c>
       <c r="N6" t="n">
-        <v>30.73780039373132</v>
+        <v>31.22112087049809</v>
       </c>
       <c r="O6" t="n">
-        <v>5.544168142628011</v>
+        <v>5.587586318840908</v>
       </c>
       <c r="P6" t="n">
-        <v>341.9295503466949</v>
+        <v>342.044085246606</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35445,28 +35637,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2305594395870928</v>
+        <v>0.2199087621251933</v>
       </c>
       <c r="J7" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K7" t="n">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07803361222698657</v>
+        <v>0.07127863902631815</v>
       </c>
       <c r="M7" t="n">
-        <v>4.989899179156445</v>
+        <v>5.02142900626366</v>
       </c>
       <c r="N7" t="n">
-        <v>38.08419451468809</v>
+        <v>38.44970168531589</v>
       </c>
       <c r="O7" t="n">
-        <v>6.171239301363065</v>
+        <v>6.20078234461716</v>
       </c>
       <c r="P7" t="n">
-        <v>341.1923790784472</v>
+        <v>341.2999380783686</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35523,28 +35715,28 @@
         <v>0.0935</v>
       </c>
       <c r="I8" t="n">
-        <v>0.202478413952566</v>
+        <v>0.1944181123152635</v>
       </c>
       <c r="J8" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K8" t="n">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06024905266463099</v>
+        <v>0.05598658986856797</v>
       </c>
       <c r="M8" t="n">
-        <v>5.106523504707443</v>
+        <v>5.119243157969976</v>
       </c>
       <c r="N8" t="n">
-        <v>38.7762308273831</v>
+        <v>38.89103162192021</v>
       </c>
       <c r="O8" t="n">
-        <v>6.227056353316798</v>
+        <v>6.236267443104105</v>
       </c>
       <c r="P8" t="n">
-        <v>346.4187744054381</v>
+        <v>346.5001752287379</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35601,28 +35793,28 @@
         <v>0.0954</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2530226274233081</v>
+        <v>0.2454094133711181</v>
       </c>
       <c r="J9" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K9" t="n">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08113254362682321</v>
+        <v>0.07705883346146003</v>
       </c>
       <c r="M9" t="n">
-        <v>5.490386797860821</v>
+        <v>5.503955781795808</v>
       </c>
       <c r="N9" t="n">
-        <v>43.96651904593437</v>
+        <v>44.01653917817787</v>
       </c>
       <c r="O9" t="n">
-        <v>6.630725378564126</v>
+        <v>6.634496151041001</v>
       </c>
       <c r="P9" t="n">
-        <v>342.71280887266</v>
+        <v>342.7896945541621</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35679,28 +35871,28 @@
         <v>0.0872</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3187868759093856</v>
+        <v>0.3106799806081842</v>
       </c>
       <c r="J10" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K10" t="n">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1164143194256478</v>
+        <v>0.1116866213662842</v>
       </c>
       <c r="M10" t="n">
-        <v>5.752887343112115</v>
+        <v>5.766519725647219</v>
       </c>
       <c r="N10" t="n">
-        <v>46.77229872505183</v>
+        <v>46.84610197698625</v>
       </c>
       <c r="O10" t="n">
-        <v>6.839027615461998</v>
+        <v>6.844421230241915</v>
       </c>
       <c r="P10" t="n">
-        <v>342.0501563015303</v>
+        <v>342.1320271072261</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35757,28 +35949,28 @@
         <v>0.0772</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3637457810543621</v>
+        <v>0.3541550596219488</v>
       </c>
       <c r="J11" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K11" t="n">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1305073963665349</v>
+        <v>0.1249021750423126</v>
       </c>
       <c r="M11" t="n">
-        <v>6.09283159301241</v>
+        <v>6.112859593044048</v>
       </c>
       <c r="N11" t="n">
-        <v>53.45302380058988</v>
+        <v>53.62352700756275</v>
       </c>
       <c r="O11" t="n">
-        <v>7.311157487059753</v>
+        <v>7.322808682982422</v>
       </c>
       <c r="P11" t="n">
-        <v>347.2091259772309</v>
+        <v>347.3059827359069</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35835,28 +36027,28 @@
         <v>0.0689</v>
       </c>
       <c r="I12" t="n">
-        <v>0.407013225727138</v>
+        <v>0.3971745904237172</v>
       </c>
       <c r="J12" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K12" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1492344058012879</v>
+        <v>0.1435293872121748</v>
       </c>
       <c r="M12" t="n">
-        <v>6.229217122551582</v>
+        <v>6.244282266869703</v>
       </c>
       <c r="N12" t="n">
-        <v>57.06759184503418</v>
+        <v>57.24229763948645</v>
       </c>
       <c r="O12" t="n">
-        <v>7.554309488300977</v>
+        <v>7.565863971780517</v>
       </c>
       <c r="P12" t="n">
-        <v>349.8926444493769</v>
+        <v>349.9921435397378</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35913,28 +36105,28 @@
         <v>0.0612</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3965586845535288</v>
+        <v>0.3875760508548088</v>
       </c>
       <c r="J13" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K13" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09573672466529493</v>
+        <v>0.0924549364056293</v>
       </c>
       <c r="M13" t="n">
-        <v>7.746848510865068</v>
+        <v>7.747190538419711</v>
       </c>
       <c r="N13" t="n">
-        <v>89.75585824684458</v>
+        <v>89.66737799524442</v>
       </c>
       <c r="O13" t="n">
-        <v>9.473956842145977</v>
+        <v>9.469286034081156</v>
       </c>
       <c r="P13" t="n">
-        <v>338.6594240061459</v>
+        <v>338.7502662061236</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35991,28 +36183,28 @@
         <v>0.0467</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2387356079270548</v>
+        <v>0.2330981072628262</v>
       </c>
       <c r="J14" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K14" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02190004501990139</v>
+        <v>0.02112238812415612</v>
       </c>
       <c r="M14" t="n">
-        <v>10.27980259711617</v>
+        <v>10.24817061314303</v>
       </c>
       <c r="N14" t="n">
-        <v>153.8169432084899</v>
+        <v>153.1247458432117</v>
       </c>
       <c r="O14" t="n">
-        <v>12.40229588457274</v>
+        <v>12.37435840127526</v>
       </c>
       <c r="P14" t="n">
-        <v>327.7326913265157</v>
+        <v>327.7897015486436</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36069,28 +36261,28 @@
         <v>0.0581</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1919368034726161</v>
+        <v>0.1858782458338435</v>
       </c>
       <c r="J15" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K15" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04173062625193757</v>
+        <v>0.03955066589641831</v>
       </c>
       <c r="M15" t="n">
-        <v>5.928109344330484</v>
+        <v>5.925370517973944</v>
       </c>
       <c r="N15" t="n">
-        <v>51.11881375267468</v>
+        <v>51.02233147589978</v>
       </c>
       <c r="O15" t="n">
-        <v>7.14974221581972</v>
+        <v>7.142991773472778</v>
       </c>
       <c r="P15" t="n">
-        <v>334.1460658806752</v>
+        <v>334.2073352229538</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36128,7 +36320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P537"/>
+  <dimension ref="A1:P540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80117,6 +80309,252 @@
         </is>
       </c>
     </row>
+    <row r="538">
+      <c r="A538" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>-34.989915957208275,173.70974816148902</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>-34.99066752273319,173.70968394085438</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>-34.9914152199938,173.70986983612784</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>-34.992142689598886,173.71021359912137</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>-34.99282226149718,173.7106629088123</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>-34.99340371036618,173.71121833762604</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>-34.99395459747089,173.71184574948256</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>-34.99447744733902,173.7125009450183</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>-34.99497728759812,173.71315531199033</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>-34.99546198839875,173.7138359020866</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>-34.99593714654336,173.71453729881011</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>-34.996425910255134,173.7152339635601</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>-34.996920690336,173.71592174475177</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>-34.99726566410445,173.71672317262906</t>
+        </is>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>-34.98991558637371,173.70976086338024</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>-34.990666851793996,173.70969398817394</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>-34.99141416680927,173.70987639622717</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>-34.99214181961789,173.71021576550018</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>-34.992818885262245,173.71066832349703</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>-34.99340200055055,173.71122102480504</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>-34.99395227012468,173.71184880539442</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>-34.994475466692776,173.71250318394027</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>-34.994974879707875,173.71315811825332</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>-34.99546212047593,173.71383575286802</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>-34.99593240036214,173.71454166186314</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>-34.99641780626807,173.7152403260982</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>-34.99691655439946,173.71592486740167</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>-34.997260399422316,173.7167269922088</t>
+        </is>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>-34.98991535300299,173.7097688568117</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>-34.99066625378229,173.70970294339335</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>-34.99141240574582,173.70988736557317</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>-34.99214079145849,173.71021832576594</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>-34.99281518229462,173.71067426218295</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>-34.993401559307785,173.7112217182706</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>-34.99395594488184,173.71184398027034</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>-34.99447896583445,173.71249922851138</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>-34.994977352676244,173.7131552361454</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>-34.99546575259817,173.7138316493559</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>-34.99592887668205,173.7145449010992</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>-34.99641629150409,173.71524151535755</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>-34.996907899569024,173.7159314018346</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>-34.99725490247467,173.71673098029888</t>
+        </is>
+      </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
